--- a/e2e-screenshots/report-round-trip/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/report-round-trip/downloaded-inventory-report.xlsx
@@ -1142,7 +1142,7 @@
         <v>21</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1180,7 +1180,7 @@
         <v>21</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1218,7 +1218,7 @@
         <v>21</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -1256,7 +1256,7 @@
         <v>21</v>
       </c>
       <c r="L5">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1294,7 +1294,7 @@
         <v>21</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1332,7 +1332,7 @@
         <v>21</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1370,7 +1370,7 @@
         <v>21</v>
       </c>
       <c r="L8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -1408,7 +1408,7 @@
         <v>21</v>
       </c>
       <c r="L9">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1446,7 +1446,7 @@
         <v>21</v>
       </c>
       <c r="L10">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1484,7 +1484,7 @@
         <v>21</v>
       </c>
       <c r="L11">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1522,7 +1522,7 @@
         <v>21</v>
       </c>
       <c r="L12">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1560,7 +1560,7 @@
         <v>21</v>
       </c>
       <c r="L13">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1598,7 +1598,7 @@
         <v>21</v>
       </c>
       <c r="L14">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1636,7 +1636,7 @@
         <v>21</v>
       </c>
       <c r="L15">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1674,7 +1674,7 @@
         <v>21</v>
       </c>
       <c r="L16">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -1712,7 +1712,7 @@
         <v>21</v>
       </c>
       <c r="L17">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1750,7 +1750,7 @@
         <v>21</v>
       </c>
       <c r="L18">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1788,7 +1788,7 @@
         <v>21</v>
       </c>
       <c r="L19">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -1826,7 +1826,7 @@
         <v>21</v>
       </c>
       <c r="L20">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -1864,7 +1864,7 @@
         <v>21</v>
       </c>
       <c r="L21">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -1902,7 +1902,7 @@
         <v>21</v>
       </c>
       <c r="L22">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -1940,7 +1940,7 @@
         <v>21</v>
       </c>
       <c r="L23">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -1978,7 +1978,7 @@
         <v>21</v>
       </c>
       <c r="L24">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -2016,7 +2016,7 @@
         <v>21</v>
       </c>
       <c r="L25">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -2054,7 +2054,7 @@
         <v>21</v>
       </c>
       <c r="L26">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -2092,7 +2092,7 @@
         <v>21</v>
       </c>
       <c r="L27">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -2130,7 +2130,7 @@
         <v>21</v>
       </c>
       <c r="L28">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -2168,7 +2168,7 @@
         <v>21</v>
       </c>
       <c r="L29">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -2206,7 +2206,7 @@
         <v>21</v>
       </c>
       <c r="L30">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -2244,7 +2244,7 @@
         <v>21</v>
       </c>
       <c r="L31">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -2282,7 +2282,7 @@
         <v>21</v>
       </c>
       <c r="L32">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -2320,7 +2320,7 @@
         <v>21</v>
       </c>
       <c r="L33">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -2358,7 +2358,7 @@
         <v>21</v>
       </c>
       <c r="L34">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -2396,7 +2396,7 @@
         <v>21</v>
       </c>
       <c r="L35">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -2434,7 +2434,7 @@
         <v>21</v>
       </c>
       <c r="L36">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -2472,7 +2472,7 @@
         <v>21</v>
       </c>
       <c r="L37">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -2510,7 +2510,7 @@
         <v>21</v>
       </c>
       <c r="L38">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -2548,7 +2548,7 @@
         <v>21</v>
       </c>
       <c r="L39">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -2586,7 +2586,7 @@
         <v>21</v>
       </c>
       <c r="L40">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -2624,7 +2624,7 @@
         <v>21</v>
       </c>
       <c r="L41">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -2662,7 +2662,7 @@
         <v>21</v>
       </c>
       <c r="L42">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -2700,7 +2700,7 @@
         <v>21</v>
       </c>
       <c r="L43">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -2738,7 +2738,7 @@
         <v>21</v>
       </c>
       <c r="L44">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -2776,7 +2776,7 @@
         <v>21</v>
       </c>
       <c r="L45">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -2814,7 +2814,7 @@
         <v>21</v>
       </c>
       <c r="L46">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -2852,7 +2852,7 @@
         <v>21</v>
       </c>
       <c r="L47">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -2890,7 +2890,7 @@
         <v>21</v>
       </c>
       <c r="L48">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -2928,7 +2928,7 @@
         <v>21</v>
       </c>
       <c r="L49">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -2966,7 +2966,7 @@
         <v>21</v>
       </c>
       <c r="L50">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -3004,7 +3004,7 @@
         <v>21</v>
       </c>
       <c r="L51">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -3042,7 +3042,7 @@
         <v>21</v>
       </c>
       <c r="L52">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -3080,7 +3080,7 @@
         <v>21</v>
       </c>
       <c r="L53">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -3118,7 +3118,7 @@
         <v>21</v>
       </c>
       <c r="L54">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -3156,7 +3156,7 @@
         <v>21</v>
       </c>
       <c r="L55">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -3194,7 +3194,7 @@
         <v>21</v>
       </c>
       <c r="L56">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -3232,7 +3232,7 @@
         <v>21</v>
       </c>
       <c r="L57">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -3270,7 +3270,7 @@
         <v>21</v>
       </c>
       <c r="L58">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -3308,7 +3308,7 @@
         <v>21</v>
       </c>
       <c r="L59">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -3346,7 +3346,7 @@
         <v>21</v>
       </c>
       <c r="L60">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -3384,7 +3384,7 @@
         <v>21</v>
       </c>
       <c r="L61">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -3422,7 +3422,7 @@
         <v>21</v>
       </c>
       <c r="L62">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -3460,7 +3460,7 @@
         <v>21</v>
       </c>
       <c r="L63">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -3498,7 +3498,7 @@
         <v>21</v>
       </c>
       <c r="L64">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -3536,7 +3536,7 @@
         <v>21</v>
       </c>
       <c r="L65">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -3574,7 +3574,7 @@
         <v>21</v>
       </c>
       <c r="L66">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -3612,7 +3612,7 @@
         <v>21</v>
       </c>
       <c r="L67">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -3650,7 +3650,7 @@
         <v>21</v>
       </c>
       <c r="L68">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -3688,7 +3688,7 @@
         <v>21</v>
       </c>
       <c r="L69">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -3726,7 +3726,7 @@
         <v>21</v>
       </c>
       <c r="L70">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -3764,7 +3764,7 @@
         <v>21</v>
       </c>
       <c r="L71">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -3802,7 +3802,7 @@
         <v>21</v>
       </c>
       <c r="L72">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -3840,7 +3840,7 @@
         <v>21</v>
       </c>
       <c r="L73">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -3878,7 +3878,7 @@
         <v>21</v>
       </c>
       <c r="L74">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -3916,7 +3916,7 @@
         <v>21</v>
       </c>
       <c r="L75">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -3954,7 +3954,7 @@
         <v>21</v>
       </c>
       <c r="L76">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -3992,7 +3992,7 @@
         <v>21</v>
       </c>
       <c r="L77">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -4030,7 +4030,7 @@
         <v>21</v>
       </c>
       <c r="L78">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -4068,7 +4068,7 @@
         <v>21</v>
       </c>
       <c r="L79">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -4106,7 +4106,7 @@
         <v>21</v>
       </c>
       <c r="L80">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -4144,7 +4144,7 @@
         <v>21</v>
       </c>
       <c r="L81">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -4182,7 +4182,7 @@
         <v>21</v>
       </c>
       <c r="L82">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -4220,7 +4220,7 @@
         <v>21</v>
       </c>
       <c r="L83">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -4258,7 +4258,7 @@
         <v>21</v>
       </c>
       <c r="L84">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -4296,7 +4296,7 @@
         <v>21</v>
       </c>
       <c r="L85">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -4334,7 +4334,7 @@
         <v>21</v>
       </c>
       <c r="L86">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -4372,7 +4372,7 @@
         <v>21</v>
       </c>
       <c r="L87">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -4410,7 +4410,7 @@
         <v>21</v>
       </c>
       <c r="L88">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -4448,7 +4448,7 @@
         <v>21</v>
       </c>
       <c r="L89">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -4486,7 +4486,7 @@
         <v>21</v>
       </c>
       <c r="L90">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -4524,7 +4524,7 @@
         <v>21</v>
       </c>
       <c r="L91">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -4562,7 +4562,7 @@
         <v>21</v>
       </c>
       <c r="L92">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -4600,7 +4600,7 @@
         <v>21</v>
       </c>
       <c r="L93">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -4638,7 +4638,7 @@
         <v>21</v>
       </c>
       <c r="L94">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -4676,7 +4676,7 @@
         <v>21</v>
       </c>
       <c r="L95">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -4714,7 +4714,7 @@
         <v>21</v>
       </c>
       <c r="L96">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -4752,7 +4752,7 @@
         <v>21</v>
       </c>
       <c r="L97">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4790,7 +4790,7 @@
         <v>21</v>
       </c>
       <c r="L98">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -4828,7 +4828,7 @@
         <v>21</v>
       </c>
       <c r="L99">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -4866,7 +4866,7 @@
         <v>21</v>
       </c>
       <c r="L100">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4904,7 +4904,7 @@
         <v>21</v>
       </c>
       <c r="L101">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4942,7 +4942,7 @@
         <v>21</v>
       </c>
       <c r="L102">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4980,7 +4980,7 @@
         <v>21</v>
       </c>
       <c r="L103">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -5018,7 +5018,7 @@
         <v>21</v>
       </c>
       <c r="L104">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -5056,7 +5056,7 @@
         <v>21</v>
       </c>
       <c r="L105">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -5094,7 +5094,7 @@
         <v>21</v>
       </c>
       <c r="L106">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -5132,7 +5132,7 @@
         <v>21</v>
       </c>
       <c r="L107">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -5170,7 +5170,7 @@
         <v>21</v>
       </c>
       <c r="L108">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -5208,7 +5208,7 @@
         <v>21</v>
       </c>
       <c r="L109">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -5246,7 +5246,7 @@
         <v>21</v>
       </c>
       <c r="L110">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -5284,7 +5284,7 @@
         <v>21</v>
       </c>
       <c r="L111">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -5379,7 +5379,7 @@
         <v>207</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -5417,7 +5417,7 @@
         <v>207</v>
       </c>
       <c r="L3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -5455,7 +5455,7 @@
         <v>207</v>
       </c>
       <c r="L4">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -5493,7 +5493,7 @@
         <v>207</v>
       </c>
       <c r="L5">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -5531,7 +5531,7 @@
         <v>207</v>
       </c>
       <c r="L6">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -5569,7 +5569,7 @@
         <v>207</v>
       </c>
       <c r="L7">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -5607,7 +5607,7 @@
         <v>207</v>
       </c>
       <c r="L8">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -5645,7 +5645,7 @@
         <v>207</v>
       </c>
       <c r="L9">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -5683,7 +5683,7 @@
         <v>207</v>
       </c>
       <c r="L10">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -5721,7 +5721,7 @@
         <v>207</v>
       </c>
       <c r="L11">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/e2e-screenshots/report-round-trip/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/report-round-trip/downloaded-inventory-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="207">
   <si>
     <t>Stock In Date</t>
   </si>
@@ -629,40 +629,10 @@
     <t>350100000791900</t>
   </si>
   <si>
-    <t>350100000380112</t>
-  </si>
-  <si>
     <t>SHS</t>
   </si>
   <si>
     <t>Supplier holding — awaiting delivery</t>
-  </si>
-  <si>
-    <t>350100000760224</t>
-  </si>
-  <si>
-    <t>350100000285084</t>
-  </si>
-  <si>
-    <t>350100000665196</t>
-  </si>
-  <si>
-    <t>350100000190056</t>
-  </si>
-  <si>
-    <t>350100000570168</t>
-  </si>
-  <si>
-    <t>350100000095028</t>
-  </si>
-  <si>
-    <t>350100000475140</t>
-  </si>
-  <si>
-    <t>350100000855252</t>
-  </si>
-  <si>
-    <t>350100000000000</t>
   </si>
 </sst>
 </file>
@@ -5352,7 +5322,7 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
         <v>38</v>
@@ -5373,10 +5343,10 @@
         <v>209.91</v>
       </c>
       <c r="J2" t="s">
+        <v>205</v>
+      </c>
+      <c r="K2" t="s">
         <v>206</v>
-      </c>
-      <c r="K2" t="s">
-        <v>207</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -5390,7 +5360,7 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
@@ -5411,10 +5381,10 @@
         <v>201.45</v>
       </c>
       <c r="J3" t="s">
+        <v>205</v>
+      </c>
+      <c r="K3" t="s">
         <v>206</v>
-      </c>
-      <c r="K3" t="s">
-        <v>207</v>
       </c>
       <c r="L3">
         <v>9</v>
@@ -5428,7 +5398,7 @@
         <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
         <v>24</v>
@@ -5449,10 +5419,10 @@
         <v>493.73</v>
       </c>
       <c r="J4" t="s">
+        <v>205</v>
+      </c>
+      <c r="K4" t="s">
         <v>206</v>
-      </c>
-      <c r="K4" t="s">
-        <v>207</v>
       </c>
       <c r="L4">
         <v>19</v>
@@ -5466,7 +5436,7 @@
         <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
         <v>38</v>
@@ -5487,10 +5457,10 @@
         <v>487.74</v>
       </c>
       <c r="J5" t="s">
+        <v>205</v>
+      </c>
+      <c r="K5" t="s">
         <v>206</v>
-      </c>
-      <c r="K5" t="s">
-        <v>207</v>
       </c>
       <c r="L5">
         <v>21</v>
@@ -5504,7 +5474,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
         <v>38</v>
@@ -5525,10 +5495,10 @@
         <v>190.06</v>
       </c>
       <c r="J6" t="s">
+        <v>205</v>
+      </c>
+      <c r="K6" t="s">
         <v>206</v>
-      </c>
-      <c r="K6" t="s">
-        <v>207</v>
       </c>
       <c r="L6">
         <v>31</v>
@@ -5542,7 +5512,7 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
@@ -5563,10 +5533,10 @@
         <v>208.52</v>
       </c>
       <c r="J7" t="s">
+        <v>205</v>
+      </c>
+      <c r="K7" t="s">
         <v>206</v>
-      </c>
-      <c r="K7" t="s">
-        <v>207</v>
       </c>
       <c r="L7">
         <v>33</v>
@@ -5580,7 +5550,7 @@
         <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
         <v>38</v>
@@ -5601,10 +5571,10 @@
         <v>464.55</v>
       </c>
       <c r="J8" t="s">
+        <v>205</v>
+      </c>
+      <c r="K8" t="s">
         <v>206</v>
-      </c>
-      <c r="K8" t="s">
-        <v>207</v>
       </c>
       <c r="L8">
         <v>43</v>
@@ -5618,7 +5588,7 @@
         <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>214</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
         <v>42</v>
@@ -5639,10 +5609,10 @@
         <v>480.01</v>
       </c>
       <c r="J9" t="s">
+        <v>205</v>
+      </c>
+      <c r="K9" t="s">
         <v>206</v>
-      </c>
-      <c r="K9" t="s">
-        <v>207</v>
       </c>
       <c r="L9">
         <v>45</v>
@@ -5656,7 +5626,7 @@
         <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>215</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
         <v>15</v>
@@ -5677,10 +5647,10 @@
         <v>470.62</v>
       </c>
       <c r="J10" t="s">
+        <v>205</v>
+      </c>
+      <c r="K10" t="s">
         <v>206</v>
-      </c>
-      <c r="K10" t="s">
-        <v>207</v>
       </c>
       <c r="L10">
         <v>47</v>
@@ -5694,7 +5664,7 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>216</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
         <v>35</v>
@@ -5715,10 +5685,10 @@
         <v>206.45</v>
       </c>
       <c r="J11" t="s">
+        <v>205</v>
+      </c>
+      <c r="K11" t="s">
         <v>206</v>
-      </c>
-      <c r="K11" t="s">
-        <v>207</v>
       </c>
       <c r="L11">
         <v>55</v>

--- a/e2e-screenshots/report-round-trip/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/report-round-trip/downloaded-inventory-report.xlsx
@@ -1112,7 +1112,7 @@
         <v>21</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1150,7 +1150,7 @@
         <v>21</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1188,7 +1188,7 @@
         <v>21</v>
       </c>
       <c r="L4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -1226,7 +1226,7 @@
         <v>21</v>
       </c>
       <c r="L5">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1264,7 +1264,7 @@
         <v>21</v>
       </c>
       <c r="L6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1302,7 +1302,7 @@
         <v>21</v>
       </c>
       <c r="L7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1340,7 +1340,7 @@
         <v>21</v>
       </c>
       <c r="L8">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -1378,7 +1378,7 @@
         <v>21</v>
       </c>
       <c r="L9">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1416,7 +1416,7 @@
         <v>21</v>
       </c>
       <c r="L10">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1454,7 +1454,7 @@
         <v>21</v>
       </c>
       <c r="L11">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1492,7 +1492,7 @@
         <v>21</v>
       </c>
       <c r="L12">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1530,7 +1530,7 @@
         <v>21</v>
       </c>
       <c r="L13">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1568,7 +1568,7 @@
         <v>21</v>
       </c>
       <c r="L14">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1606,7 +1606,7 @@
         <v>21</v>
       </c>
       <c r="L15">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1644,7 +1644,7 @@
         <v>21</v>
       </c>
       <c r="L16">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -1682,7 +1682,7 @@
         <v>21</v>
       </c>
       <c r="L17">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1720,7 +1720,7 @@
         <v>21</v>
       </c>
       <c r="L18">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1758,7 +1758,7 @@
         <v>21</v>
       </c>
       <c r="L19">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -1796,7 +1796,7 @@
         <v>21</v>
       </c>
       <c r="L20">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -1834,7 +1834,7 @@
         <v>21</v>
       </c>
       <c r="L21">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -1872,7 +1872,7 @@
         <v>21</v>
       </c>
       <c r="L22">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -1910,7 +1910,7 @@
         <v>21</v>
       </c>
       <c r="L23">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -1948,7 +1948,7 @@
         <v>21</v>
       </c>
       <c r="L24">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -1986,7 +1986,7 @@
         <v>21</v>
       </c>
       <c r="L25">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -2024,7 +2024,7 @@
         <v>21</v>
       </c>
       <c r="L26">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -2062,7 +2062,7 @@
         <v>21</v>
       </c>
       <c r="L27">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -2100,7 +2100,7 @@
         <v>21</v>
       </c>
       <c r="L28">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -2138,7 +2138,7 @@
         <v>21</v>
       </c>
       <c r="L29">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -2176,7 +2176,7 @@
         <v>21</v>
       </c>
       <c r="L30">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -2214,7 +2214,7 @@
         <v>21</v>
       </c>
       <c r="L31">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -2252,7 +2252,7 @@
         <v>21</v>
       </c>
       <c r="L32">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -2290,7 +2290,7 @@
         <v>21</v>
       </c>
       <c r="L33">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -2328,7 +2328,7 @@
         <v>21</v>
       </c>
       <c r="L34">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -2366,7 +2366,7 @@
         <v>21</v>
       </c>
       <c r="L35">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -2404,7 +2404,7 @@
         <v>21</v>
       </c>
       <c r="L36">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -2442,7 +2442,7 @@
         <v>21</v>
       </c>
       <c r="L37">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -2480,7 +2480,7 @@
         <v>21</v>
       </c>
       <c r="L38">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -2518,7 +2518,7 @@
         <v>21</v>
       </c>
       <c r="L39">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -2556,7 +2556,7 @@
         <v>21</v>
       </c>
       <c r="L40">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -2594,7 +2594,7 @@
         <v>21</v>
       </c>
       <c r="L41">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -2632,7 +2632,7 @@
         <v>21</v>
       </c>
       <c r="L42">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -2670,7 +2670,7 @@
         <v>21</v>
       </c>
       <c r="L43">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -2708,7 +2708,7 @@
         <v>21</v>
       </c>
       <c r="L44">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -2746,7 +2746,7 @@
         <v>21</v>
       </c>
       <c r="L45">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -2784,7 +2784,7 @@
         <v>21</v>
       </c>
       <c r="L46">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -2822,7 +2822,7 @@
         <v>21</v>
       </c>
       <c r="L47">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -2860,7 +2860,7 @@
         <v>21</v>
       </c>
       <c r="L48">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -2898,7 +2898,7 @@
         <v>21</v>
       </c>
       <c r="L49">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -2936,7 +2936,7 @@
         <v>21</v>
       </c>
       <c r="L50">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -2974,7 +2974,7 @@
         <v>21</v>
       </c>
       <c r="L51">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -3012,7 +3012,7 @@
         <v>21</v>
       </c>
       <c r="L52">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -3050,7 +3050,7 @@
         <v>21</v>
       </c>
       <c r="L53">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -3088,7 +3088,7 @@
         <v>21</v>
       </c>
       <c r="L54">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -3126,7 +3126,7 @@
         <v>21</v>
       </c>
       <c r="L55">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -3164,7 +3164,7 @@
         <v>21</v>
       </c>
       <c r="L56">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -3202,7 +3202,7 @@
         <v>21</v>
       </c>
       <c r="L57">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -3240,7 +3240,7 @@
         <v>21</v>
       </c>
       <c r="L58">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -3278,7 +3278,7 @@
         <v>21</v>
       </c>
       <c r="L59">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -3316,7 +3316,7 @@
         <v>21</v>
       </c>
       <c r="L60">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -3354,7 +3354,7 @@
         <v>21</v>
       </c>
       <c r="L61">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -3392,7 +3392,7 @@
         <v>21</v>
       </c>
       <c r="L62">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -3430,7 +3430,7 @@
         <v>21</v>
       </c>
       <c r="L63">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -3468,7 +3468,7 @@
         <v>21</v>
       </c>
       <c r="L64">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -3506,7 +3506,7 @@
         <v>21</v>
       </c>
       <c r="L65">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -3544,7 +3544,7 @@
         <v>21</v>
       </c>
       <c r="L66">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -3582,7 +3582,7 @@
         <v>21</v>
       </c>
       <c r="L67">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -3620,7 +3620,7 @@
         <v>21</v>
       </c>
       <c r="L68">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -3658,7 +3658,7 @@
         <v>21</v>
       </c>
       <c r="L69">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -3696,7 +3696,7 @@
         <v>21</v>
       </c>
       <c r="L70">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -3734,7 +3734,7 @@
         <v>21</v>
       </c>
       <c r="L71">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -3772,7 +3772,7 @@
         <v>21</v>
       </c>
       <c r="L72">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -3810,7 +3810,7 @@
         <v>21</v>
       </c>
       <c r="L73">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -3848,7 +3848,7 @@
         <v>21</v>
       </c>
       <c r="L74">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -3886,7 +3886,7 @@
         <v>21</v>
       </c>
       <c r="L75">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -3924,7 +3924,7 @@
         <v>21</v>
       </c>
       <c r="L76">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -3962,7 +3962,7 @@
         <v>21</v>
       </c>
       <c r="L77">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -4000,7 +4000,7 @@
         <v>21</v>
       </c>
       <c r="L78">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -4038,7 +4038,7 @@
         <v>21</v>
       </c>
       <c r="L79">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -4076,7 +4076,7 @@
         <v>21</v>
       </c>
       <c r="L80">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -4114,7 +4114,7 @@
         <v>21</v>
       </c>
       <c r="L81">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -4152,7 +4152,7 @@
         <v>21</v>
       </c>
       <c r="L82">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -4190,7 +4190,7 @@
         <v>21</v>
       </c>
       <c r="L83">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -4228,7 +4228,7 @@
         <v>21</v>
       </c>
       <c r="L84">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -4266,7 +4266,7 @@
         <v>21</v>
       </c>
       <c r="L85">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -4304,7 +4304,7 @@
         <v>21</v>
       </c>
       <c r="L86">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -4342,7 +4342,7 @@
         <v>21</v>
       </c>
       <c r="L87">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -4380,7 +4380,7 @@
         <v>21</v>
       </c>
       <c r="L88">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -4418,7 +4418,7 @@
         <v>21</v>
       </c>
       <c r="L89">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -4456,7 +4456,7 @@
         <v>21</v>
       </c>
       <c r="L90">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -4494,7 +4494,7 @@
         <v>21</v>
       </c>
       <c r="L91">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -4532,7 +4532,7 @@
         <v>21</v>
       </c>
       <c r="L92">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -4570,7 +4570,7 @@
         <v>21</v>
       </c>
       <c r="L93">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -4608,7 +4608,7 @@
         <v>21</v>
       </c>
       <c r="L94">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -4646,7 +4646,7 @@
         <v>21</v>
       </c>
       <c r="L95">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -4684,7 +4684,7 @@
         <v>21</v>
       </c>
       <c r="L96">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -4722,7 +4722,7 @@
         <v>21</v>
       </c>
       <c r="L97">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4760,7 +4760,7 @@
         <v>21</v>
       </c>
       <c r="L98">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -4798,7 +4798,7 @@
         <v>21</v>
       </c>
       <c r="L99">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -4836,7 +4836,7 @@
         <v>21</v>
       </c>
       <c r="L100">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4874,7 +4874,7 @@
         <v>21</v>
       </c>
       <c r="L101">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4912,7 +4912,7 @@
         <v>21</v>
       </c>
       <c r="L102">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4950,7 +4950,7 @@
         <v>21</v>
       </c>
       <c r="L103">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4988,7 +4988,7 @@
         <v>21</v>
       </c>
       <c r="L104">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -5026,7 +5026,7 @@
         <v>21</v>
       </c>
       <c r="L105">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -5064,7 +5064,7 @@
         <v>21</v>
       </c>
       <c r="L106">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -5102,7 +5102,7 @@
         <v>21</v>
       </c>
       <c r="L107">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -5140,7 +5140,7 @@
         <v>21</v>
       </c>
       <c r="L108">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -5178,7 +5178,7 @@
         <v>21</v>
       </c>
       <c r="L109">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -5216,7 +5216,7 @@
         <v>21</v>
       </c>
       <c r="L110">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -5254,7 +5254,7 @@
         <v>21</v>
       </c>
       <c r="L111">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -5349,7 +5349,7 @@
         <v>206</v>
       </c>
       <c r="L2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -5387,7 +5387,7 @@
         <v>206</v>
       </c>
       <c r="L3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -5425,7 +5425,7 @@
         <v>206</v>
       </c>
       <c r="L4">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -5463,7 +5463,7 @@
         <v>206</v>
       </c>
       <c r="L5">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -5501,7 +5501,7 @@
         <v>206</v>
       </c>
       <c r="L6">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -5539,7 +5539,7 @@
         <v>206</v>
       </c>
       <c r="L7">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -5577,7 +5577,7 @@
         <v>206</v>
       </c>
       <c r="L8">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -5615,7 +5615,7 @@
         <v>206</v>
       </c>
       <c r="L9">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -5653,7 +5653,7 @@
         <v>206</v>
       </c>
       <c r="L10">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -5691,7 +5691,7 @@
         <v>206</v>
       </c>
       <c r="L11">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/e2e-screenshots/report-round-trip/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/report-round-trip/downloaded-inventory-report.xlsx
@@ -1112,7 +1112,7 @@
         <v>21</v>
       </c>
       <c r="L2">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1150,7 +1150,7 @@
         <v>21</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1188,7 +1188,7 @@
         <v>21</v>
       </c>
       <c r="L4">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -1226,7 +1226,7 @@
         <v>21</v>
       </c>
       <c r="L5">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1264,7 +1264,7 @@
         <v>21</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1302,7 +1302,7 @@
         <v>21</v>
       </c>
       <c r="L7">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1340,7 +1340,7 @@
         <v>21</v>
       </c>
       <c r="L8">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -1378,7 +1378,7 @@
         <v>21</v>
       </c>
       <c r="L9">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1416,7 +1416,7 @@
         <v>21</v>
       </c>
       <c r="L10">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1454,7 +1454,7 @@
         <v>21</v>
       </c>
       <c r="L11">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1492,7 +1492,7 @@
         <v>21</v>
       </c>
       <c r="L12">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1530,7 +1530,7 @@
         <v>21</v>
       </c>
       <c r="L13">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1568,7 +1568,7 @@
         <v>21</v>
       </c>
       <c r="L14">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1606,7 +1606,7 @@
         <v>21</v>
       </c>
       <c r="L15">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1644,7 +1644,7 @@
         <v>21</v>
       </c>
       <c r="L16">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -1682,7 +1682,7 @@
         <v>21</v>
       </c>
       <c r="L17">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1720,7 +1720,7 @@
         <v>21</v>
       </c>
       <c r="L18">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1758,7 +1758,7 @@
         <v>21</v>
       </c>
       <c r="L19">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -1796,7 +1796,7 @@
         <v>21</v>
       </c>
       <c r="L20">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -1834,7 +1834,7 @@
         <v>21</v>
       </c>
       <c r="L21">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -1872,7 +1872,7 @@
         <v>21</v>
       </c>
       <c r="L22">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -1910,7 +1910,7 @@
         <v>21</v>
       </c>
       <c r="L23">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -1948,7 +1948,7 @@
         <v>21</v>
       </c>
       <c r="L24">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -1986,7 +1986,7 @@
         <v>21</v>
       </c>
       <c r="L25">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -2024,7 +2024,7 @@
         <v>21</v>
       </c>
       <c r="L26">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -2062,7 +2062,7 @@
         <v>21</v>
       </c>
       <c r="L27">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -2100,7 +2100,7 @@
         <v>21</v>
       </c>
       <c r="L28">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -2138,7 +2138,7 @@
         <v>21</v>
       </c>
       <c r="L29">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -2176,7 +2176,7 @@
         <v>21</v>
       </c>
       <c r="L30">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -2214,7 +2214,7 @@
         <v>21</v>
       </c>
       <c r="L31">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -2252,7 +2252,7 @@
         <v>21</v>
       </c>
       <c r="L32">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -2290,7 +2290,7 @@
         <v>21</v>
       </c>
       <c r="L33">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -2328,7 +2328,7 @@
         <v>21</v>
       </c>
       <c r="L34">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -2366,7 +2366,7 @@
         <v>21</v>
       </c>
       <c r="L35">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -2404,7 +2404,7 @@
         <v>21</v>
       </c>
       <c r="L36">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -2442,7 +2442,7 @@
         <v>21</v>
       </c>
       <c r="L37">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -2480,7 +2480,7 @@
         <v>21</v>
       </c>
       <c r="L38">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -2518,7 +2518,7 @@
         <v>21</v>
       </c>
       <c r="L39">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -2556,7 +2556,7 @@
         <v>21</v>
       </c>
       <c r="L40">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -2594,7 +2594,7 @@
         <v>21</v>
       </c>
       <c r="L41">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -2632,7 +2632,7 @@
         <v>21</v>
       </c>
       <c r="L42">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -2670,7 +2670,7 @@
         <v>21</v>
       </c>
       <c r="L43">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -2708,7 +2708,7 @@
         <v>21</v>
       </c>
       <c r="L44">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -2746,7 +2746,7 @@
         <v>21</v>
       </c>
       <c r="L45">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -2784,7 +2784,7 @@
         <v>21</v>
       </c>
       <c r="L46">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -2822,7 +2822,7 @@
         <v>21</v>
       </c>
       <c r="L47">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -2860,7 +2860,7 @@
         <v>21</v>
       </c>
       <c r="L48">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -2898,7 +2898,7 @@
         <v>21</v>
       </c>
       <c r="L49">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -2936,7 +2936,7 @@
         <v>21</v>
       </c>
       <c r="L50">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -2974,7 +2974,7 @@
         <v>21</v>
       </c>
       <c r="L51">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -3012,7 +3012,7 @@
         <v>21</v>
       </c>
       <c r="L52">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -3050,7 +3050,7 @@
         <v>21</v>
       </c>
       <c r="L53">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -3088,7 +3088,7 @@
         <v>21</v>
       </c>
       <c r="L54">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -3126,7 +3126,7 @@
         <v>21</v>
       </c>
       <c r="L55">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -3164,7 +3164,7 @@
         <v>21</v>
       </c>
       <c r="L56">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -3202,7 +3202,7 @@
         <v>21</v>
       </c>
       <c r="L57">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -3240,7 +3240,7 @@
         <v>21</v>
       </c>
       <c r="L58">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -3278,7 +3278,7 @@
         <v>21</v>
       </c>
       <c r="L59">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -3316,7 +3316,7 @@
         <v>21</v>
       </c>
       <c r="L60">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -3354,7 +3354,7 @@
         <v>21</v>
       </c>
       <c r="L61">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -3392,7 +3392,7 @@
         <v>21</v>
       </c>
       <c r="L62">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -3430,7 +3430,7 @@
         <v>21</v>
       </c>
       <c r="L63">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -3468,7 +3468,7 @@
         <v>21</v>
       </c>
       <c r="L64">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -3506,7 +3506,7 @@
         <v>21</v>
       </c>
       <c r="L65">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -3544,7 +3544,7 @@
         <v>21</v>
       </c>
       <c r="L66">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -3582,7 +3582,7 @@
         <v>21</v>
       </c>
       <c r="L67">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -3620,7 +3620,7 @@
         <v>21</v>
       </c>
       <c r="L68">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -3658,7 +3658,7 @@
         <v>21</v>
       </c>
       <c r="L69">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -3696,7 +3696,7 @@
         <v>21</v>
       </c>
       <c r="L70">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -3734,7 +3734,7 @@
         <v>21</v>
       </c>
       <c r="L71">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -3772,7 +3772,7 @@
         <v>21</v>
       </c>
       <c r="L72">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -3810,7 +3810,7 @@
         <v>21</v>
       </c>
       <c r="L73">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -3848,7 +3848,7 @@
         <v>21</v>
       </c>
       <c r="L74">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -3886,7 +3886,7 @@
         <v>21</v>
       </c>
       <c r="L75">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -3924,7 +3924,7 @@
         <v>21</v>
       </c>
       <c r="L76">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -3962,7 +3962,7 @@
         <v>21</v>
       </c>
       <c r="L77">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -4000,7 +4000,7 @@
         <v>21</v>
       </c>
       <c r="L78">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -4038,7 +4038,7 @@
         <v>21</v>
       </c>
       <c r="L79">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -4076,7 +4076,7 @@
         <v>21</v>
       </c>
       <c r="L80">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -4114,7 +4114,7 @@
         <v>21</v>
       </c>
       <c r="L81">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -4152,7 +4152,7 @@
         <v>21</v>
       </c>
       <c r="L82">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -4190,7 +4190,7 @@
         <v>21</v>
       </c>
       <c r="L83">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -4228,7 +4228,7 @@
         <v>21</v>
       </c>
       <c r="L84">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -4266,7 +4266,7 @@
         <v>21</v>
       </c>
       <c r="L85">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -4304,7 +4304,7 @@
         <v>21</v>
       </c>
       <c r="L86">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -4342,7 +4342,7 @@
         <v>21</v>
       </c>
       <c r="L87">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -4380,7 +4380,7 @@
         <v>21</v>
       </c>
       <c r="L88">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -4418,7 +4418,7 @@
         <v>21</v>
       </c>
       <c r="L89">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -4456,7 +4456,7 @@
         <v>21</v>
       </c>
       <c r="L90">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -4494,7 +4494,7 @@
         <v>21</v>
       </c>
       <c r="L91">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -4532,7 +4532,7 @@
         <v>21</v>
       </c>
       <c r="L92">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -4570,7 +4570,7 @@
         <v>21</v>
       </c>
       <c r="L93">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -4608,7 +4608,7 @@
         <v>21</v>
       </c>
       <c r="L94">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -4646,7 +4646,7 @@
         <v>21</v>
       </c>
       <c r="L95">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -4684,7 +4684,7 @@
         <v>21</v>
       </c>
       <c r="L96">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -4722,7 +4722,7 @@
         <v>21</v>
       </c>
       <c r="L97">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4760,7 +4760,7 @@
         <v>21</v>
       </c>
       <c r="L98">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -4798,7 +4798,7 @@
         <v>21</v>
       </c>
       <c r="L99">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -4836,7 +4836,7 @@
         <v>21</v>
       </c>
       <c r="L100">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4874,7 +4874,7 @@
         <v>21</v>
       </c>
       <c r="L101">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4912,7 +4912,7 @@
         <v>21</v>
       </c>
       <c r="L102">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4950,7 +4950,7 @@
         <v>21</v>
       </c>
       <c r="L103">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4988,7 +4988,7 @@
         <v>21</v>
       </c>
       <c r="L104">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -5026,7 +5026,7 @@
         <v>21</v>
       </c>
       <c r="L105">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -5064,7 +5064,7 @@
         <v>21</v>
       </c>
       <c r="L106">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -5102,7 +5102,7 @@
         <v>21</v>
       </c>
       <c r="L107">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -5140,7 +5140,7 @@
         <v>21</v>
       </c>
       <c r="L108">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -5178,7 +5178,7 @@
         <v>21</v>
       </c>
       <c r="L109">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -5216,7 +5216,7 @@
         <v>21</v>
       </c>
       <c r="L110">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -5254,7 +5254,7 @@
         <v>21</v>
       </c>
       <c r="L111">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -5349,7 +5349,7 @@
         <v>206</v>
       </c>
       <c r="L2">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -5387,7 +5387,7 @@
         <v>206</v>
       </c>
       <c r="L3">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -5425,7 +5425,7 @@
         <v>206</v>
       </c>
       <c r="L4">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -5463,7 +5463,7 @@
         <v>206</v>
       </c>
       <c r="L5">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -5501,7 +5501,7 @@
         <v>206</v>
       </c>
       <c r="L6">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -5539,7 +5539,7 @@
         <v>206</v>
       </c>
       <c r="L7">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -5577,7 +5577,7 @@
         <v>206</v>
       </c>
       <c r="L8">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -5615,7 +5615,7 @@
         <v>206</v>
       </c>
       <c r="L9">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -5653,7 +5653,7 @@
         <v>206</v>
       </c>
       <c r="L10">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -5691,7 +5691,7 @@
         <v>206</v>
       </c>
       <c r="L11">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/e2e-screenshots/report-round-trip/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/report-round-trip/downloaded-inventory-report.xlsx
@@ -1112,7 +1112,7 @@
         <v>21</v>
       </c>
       <c r="L2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1150,7 +1150,7 @@
         <v>21</v>
       </c>
       <c r="L3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1188,7 +1188,7 @@
         <v>21</v>
       </c>
       <c r="L4">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -1226,7 +1226,7 @@
         <v>21</v>
       </c>
       <c r="L5">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1264,7 +1264,7 @@
         <v>21</v>
       </c>
       <c r="L6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1302,7 +1302,7 @@
         <v>21</v>
       </c>
       <c r="L7">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1340,7 +1340,7 @@
         <v>21</v>
       </c>
       <c r="L8">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -1378,7 +1378,7 @@
         <v>21</v>
       </c>
       <c r="L9">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1416,7 +1416,7 @@
         <v>21</v>
       </c>
       <c r="L10">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1454,7 +1454,7 @@
         <v>21</v>
       </c>
       <c r="L11">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1492,7 +1492,7 @@
         <v>21</v>
       </c>
       <c r="L12">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1530,7 +1530,7 @@
         <v>21</v>
       </c>
       <c r="L13">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1568,7 +1568,7 @@
         <v>21</v>
       </c>
       <c r="L14">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1606,7 +1606,7 @@
         <v>21</v>
       </c>
       <c r="L15">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1644,7 +1644,7 @@
         <v>21</v>
       </c>
       <c r="L16">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -1682,7 +1682,7 @@
         <v>21</v>
       </c>
       <c r="L17">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1720,7 +1720,7 @@
         <v>21</v>
       </c>
       <c r="L18">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1758,7 +1758,7 @@
         <v>21</v>
       </c>
       <c r="L19">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -1796,7 +1796,7 @@
         <v>21</v>
       </c>
       <c r="L20">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -1834,7 +1834,7 @@
         <v>21</v>
       </c>
       <c r="L21">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -1872,7 +1872,7 @@
         <v>21</v>
       </c>
       <c r="L22">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -1910,7 +1910,7 @@
         <v>21</v>
       </c>
       <c r="L23">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -1948,7 +1948,7 @@
         <v>21</v>
       </c>
       <c r="L24">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -1986,7 +1986,7 @@
         <v>21</v>
       </c>
       <c r="L25">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -2024,7 +2024,7 @@
         <v>21</v>
       </c>
       <c r="L26">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -2062,7 +2062,7 @@
         <v>21</v>
       </c>
       <c r="L27">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -2100,7 +2100,7 @@
         <v>21</v>
       </c>
       <c r="L28">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -2138,7 +2138,7 @@
         <v>21</v>
       </c>
       <c r="L29">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -2176,7 +2176,7 @@
         <v>21</v>
       </c>
       <c r="L30">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -2214,7 +2214,7 @@
         <v>21</v>
       </c>
       <c r="L31">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -2252,7 +2252,7 @@
         <v>21</v>
       </c>
       <c r="L32">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -2290,7 +2290,7 @@
         <v>21</v>
       </c>
       <c r="L33">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -2328,7 +2328,7 @@
         <v>21</v>
       </c>
       <c r="L34">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -2366,7 +2366,7 @@
         <v>21</v>
       </c>
       <c r="L35">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -2404,7 +2404,7 @@
         <v>21</v>
       </c>
       <c r="L36">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -2442,7 +2442,7 @@
         <v>21</v>
       </c>
       <c r="L37">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -2480,7 +2480,7 @@
         <v>21</v>
       </c>
       <c r="L38">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -2518,7 +2518,7 @@
         <v>21</v>
       </c>
       <c r="L39">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -2556,7 +2556,7 @@
         <v>21</v>
       </c>
       <c r="L40">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -2594,7 +2594,7 @@
         <v>21</v>
       </c>
       <c r="L41">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -2632,7 +2632,7 @@
         <v>21</v>
       </c>
       <c r="L42">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -2670,7 +2670,7 @@
         <v>21</v>
       </c>
       <c r="L43">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -2708,7 +2708,7 @@
         <v>21</v>
       </c>
       <c r="L44">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -2746,7 +2746,7 @@
         <v>21</v>
       </c>
       <c r="L45">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -2784,7 +2784,7 @@
         <v>21</v>
       </c>
       <c r="L46">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -2822,7 +2822,7 @@
         <v>21</v>
       </c>
       <c r="L47">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -2860,7 +2860,7 @@
         <v>21</v>
       </c>
       <c r="L48">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -2898,7 +2898,7 @@
         <v>21</v>
       </c>
       <c r="L49">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -2936,7 +2936,7 @@
         <v>21</v>
       </c>
       <c r="L50">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -2974,7 +2974,7 @@
         <v>21</v>
       </c>
       <c r="L51">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -3012,7 +3012,7 @@
         <v>21</v>
       </c>
       <c r="L52">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -3050,7 +3050,7 @@
         <v>21</v>
       </c>
       <c r="L53">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -3088,7 +3088,7 @@
         <v>21</v>
       </c>
       <c r="L54">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -3126,7 +3126,7 @@
         <v>21</v>
       </c>
       <c r="L55">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -3164,7 +3164,7 @@
         <v>21</v>
       </c>
       <c r="L56">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -3202,7 +3202,7 @@
         <v>21</v>
       </c>
       <c r="L57">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -3240,7 +3240,7 @@
         <v>21</v>
       </c>
       <c r="L58">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -3278,7 +3278,7 @@
         <v>21</v>
       </c>
       <c r="L59">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -3316,7 +3316,7 @@
         <v>21</v>
       </c>
       <c r="L60">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -3354,7 +3354,7 @@
         <v>21</v>
       </c>
       <c r="L61">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -3392,7 +3392,7 @@
         <v>21</v>
       </c>
       <c r="L62">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -3430,7 +3430,7 @@
         <v>21</v>
       </c>
       <c r="L63">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -3468,7 +3468,7 @@
         <v>21</v>
       </c>
       <c r="L64">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -3506,7 +3506,7 @@
         <v>21</v>
       </c>
       <c r="L65">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -3544,7 +3544,7 @@
         <v>21</v>
       </c>
       <c r="L66">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -3582,7 +3582,7 @@
         <v>21</v>
       </c>
       <c r="L67">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -3620,7 +3620,7 @@
         <v>21</v>
       </c>
       <c r="L68">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -3658,7 +3658,7 @@
         <v>21</v>
       </c>
       <c r="L69">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -3696,7 +3696,7 @@
         <v>21</v>
       </c>
       <c r="L70">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -3734,7 +3734,7 @@
         <v>21</v>
       </c>
       <c r="L71">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -3772,7 +3772,7 @@
         <v>21</v>
       </c>
       <c r="L72">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -3810,7 +3810,7 @@
         <v>21</v>
       </c>
       <c r="L73">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -3848,7 +3848,7 @@
         <v>21</v>
       </c>
       <c r="L74">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -3886,7 +3886,7 @@
         <v>21</v>
       </c>
       <c r="L75">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -3924,7 +3924,7 @@
         <v>21</v>
       </c>
       <c r="L76">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -3962,7 +3962,7 @@
         <v>21</v>
       </c>
       <c r="L77">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -4000,7 +4000,7 @@
         <v>21</v>
       </c>
       <c r="L78">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -4038,7 +4038,7 @@
         <v>21</v>
       </c>
       <c r="L79">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -4076,7 +4076,7 @@
         <v>21</v>
       </c>
       <c r="L80">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -4114,7 +4114,7 @@
         <v>21</v>
       </c>
       <c r="L81">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -4152,7 +4152,7 @@
         <v>21</v>
       </c>
       <c r="L82">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -4190,7 +4190,7 @@
         <v>21</v>
       </c>
       <c r="L83">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -4228,7 +4228,7 @@
         <v>21</v>
       </c>
       <c r="L84">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -4266,7 +4266,7 @@
         <v>21</v>
       </c>
       <c r="L85">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -4304,7 +4304,7 @@
         <v>21</v>
       </c>
       <c r="L86">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -4342,7 +4342,7 @@
         <v>21</v>
       </c>
       <c r="L87">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -4380,7 +4380,7 @@
         <v>21</v>
       </c>
       <c r="L88">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -4418,7 +4418,7 @@
         <v>21</v>
       </c>
       <c r="L89">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -4456,7 +4456,7 @@
         <v>21</v>
       </c>
       <c r="L90">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -4494,7 +4494,7 @@
         <v>21</v>
       </c>
       <c r="L91">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -4532,7 +4532,7 @@
         <v>21</v>
       </c>
       <c r="L92">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -4570,7 +4570,7 @@
         <v>21</v>
       </c>
       <c r="L93">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -4608,7 +4608,7 @@
         <v>21</v>
       </c>
       <c r="L94">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -4646,7 +4646,7 @@
         <v>21</v>
       </c>
       <c r="L95">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -4684,7 +4684,7 @@
         <v>21</v>
       </c>
       <c r="L96">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -4722,7 +4722,7 @@
         <v>21</v>
       </c>
       <c r="L97">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4760,7 +4760,7 @@
         <v>21</v>
       </c>
       <c r="L98">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -4798,7 +4798,7 @@
         <v>21</v>
       </c>
       <c r="L99">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -4836,7 +4836,7 @@
         <v>21</v>
       </c>
       <c r="L100">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4874,7 +4874,7 @@
         <v>21</v>
       </c>
       <c r="L101">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4912,7 +4912,7 @@
         <v>21</v>
       </c>
       <c r="L102">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4950,7 +4950,7 @@
         <v>21</v>
       </c>
       <c r="L103">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4988,7 +4988,7 @@
         <v>21</v>
       </c>
       <c r="L104">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -5026,7 +5026,7 @@
         <v>21</v>
       </c>
       <c r="L105">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -5064,7 +5064,7 @@
         <v>21</v>
       </c>
       <c r="L106">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -5102,7 +5102,7 @@
         <v>21</v>
       </c>
       <c r="L107">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -5140,7 +5140,7 @@
         <v>21</v>
       </c>
       <c r="L108">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -5178,7 +5178,7 @@
         <v>21</v>
       </c>
       <c r="L109">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -5216,7 +5216,7 @@
         <v>21</v>
       </c>
       <c r="L110">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -5254,7 +5254,7 @@
         <v>21</v>
       </c>
       <c r="L111">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -5349,7 +5349,7 @@
         <v>206</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -5387,7 +5387,7 @@
         <v>206</v>
       </c>
       <c r="L3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -5425,7 +5425,7 @@
         <v>206</v>
       </c>
       <c r="L4">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -5463,7 +5463,7 @@
         <v>206</v>
       </c>
       <c r="L5">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -5501,7 +5501,7 @@
         <v>206</v>
       </c>
       <c r="L6">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -5539,7 +5539,7 @@
         <v>206</v>
       </c>
       <c r="L7">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -5577,7 +5577,7 @@
         <v>206</v>
       </c>
       <c r="L8">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -5615,7 +5615,7 @@
         <v>206</v>
       </c>
       <c r="L9">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -5653,7 +5653,7 @@
         <v>206</v>
       </c>
       <c r="L10">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -5691,7 +5691,7 @@
         <v>206</v>
       </c>
       <c r="L11">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/e2e-screenshots/report-round-trip/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/report-round-trip/downloaded-inventory-report.xlsx
@@ -1112,7 +1112,7 @@
         <v>21</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1150,7 +1150,7 @@
         <v>21</v>
       </c>
       <c r="L3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1188,7 +1188,7 @@
         <v>21</v>
       </c>
       <c r="L4">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -1226,7 +1226,7 @@
         <v>21</v>
       </c>
       <c r="L5">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1264,7 +1264,7 @@
         <v>21</v>
       </c>
       <c r="L6">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1302,7 +1302,7 @@
         <v>21</v>
       </c>
       <c r="L7">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1340,7 +1340,7 @@
         <v>21</v>
       </c>
       <c r="L8">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -1378,7 +1378,7 @@
         <v>21</v>
       </c>
       <c r="L9">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1416,7 +1416,7 @@
         <v>21</v>
       </c>
       <c r="L10">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1454,7 +1454,7 @@
         <v>21</v>
       </c>
       <c r="L11">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1492,7 +1492,7 @@
         <v>21</v>
       </c>
       <c r="L12">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1530,7 +1530,7 @@
         <v>21</v>
       </c>
       <c r="L13">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1568,7 +1568,7 @@
         <v>21</v>
       </c>
       <c r="L14">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1606,7 +1606,7 @@
         <v>21</v>
       </c>
       <c r="L15">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1644,7 +1644,7 @@
         <v>21</v>
       </c>
       <c r="L16">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -1682,7 +1682,7 @@
         <v>21</v>
       </c>
       <c r="L17">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1720,7 +1720,7 @@
         <v>21</v>
       </c>
       <c r="L18">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1758,7 +1758,7 @@
         <v>21</v>
       </c>
       <c r="L19">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -1796,7 +1796,7 @@
         <v>21</v>
       </c>
       <c r="L20">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -1834,7 +1834,7 @@
         <v>21</v>
       </c>
       <c r="L21">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -1872,7 +1872,7 @@
         <v>21</v>
       </c>
       <c r="L22">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -1910,7 +1910,7 @@
         <v>21</v>
       </c>
       <c r="L23">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -1948,7 +1948,7 @@
         <v>21</v>
       </c>
       <c r="L24">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -1986,7 +1986,7 @@
         <v>21</v>
       </c>
       <c r="L25">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -2024,7 +2024,7 @@
         <v>21</v>
       </c>
       <c r="L26">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -2062,7 +2062,7 @@
         <v>21</v>
       </c>
       <c r="L27">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -2100,7 +2100,7 @@
         <v>21</v>
       </c>
       <c r="L28">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -2138,7 +2138,7 @@
         <v>21</v>
       </c>
       <c r="L29">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -2176,7 +2176,7 @@
         <v>21</v>
       </c>
       <c r="L30">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -2214,7 +2214,7 @@
         <v>21</v>
       </c>
       <c r="L31">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -2252,7 +2252,7 @@
         <v>21</v>
       </c>
       <c r="L32">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -2290,7 +2290,7 @@
         <v>21</v>
       </c>
       <c r="L33">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -2328,7 +2328,7 @@
         <v>21</v>
       </c>
       <c r="L34">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -2366,7 +2366,7 @@
         <v>21</v>
       </c>
       <c r="L35">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -2404,7 +2404,7 @@
         <v>21</v>
       </c>
       <c r="L36">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -2442,7 +2442,7 @@
         <v>21</v>
       </c>
       <c r="L37">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -2480,7 +2480,7 @@
         <v>21</v>
       </c>
       <c r="L38">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -2518,7 +2518,7 @@
         <v>21</v>
       </c>
       <c r="L39">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -2556,7 +2556,7 @@
         <v>21</v>
       </c>
       <c r="L40">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -2594,7 +2594,7 @@
         <v>21</v>
       </c>
       <c r="L41">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -2632,7 +2632,7 @@
         <v>21</v>
       </c>
       <c r="L42">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -2670,7 +2670,7 @@
         <v>21</v>
       </c>
       <c r="L43">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -2708,7 +2708,7 @@
         <v>21</v>
       </c>
       <c r="L44">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -2746,7 +2746,7 @@
         <v>21</v>
       </c>
       <c r="L45">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -2784,7 +2784,7 @@
         <v>21</v>
       </c>
       <c r="L46">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -2822,7 +2822,7 @@
         <v>21</v>
       </c>
       <c r="L47">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -2860,7 +2860,7 @@
         <v>21</v>
       </c>
       <c r="L48">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -2898,7 +2898,7 @@
         <v>21</v>
       </c>
       <c r="L49">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -2936,7 +2936,7 @@
         <v>21</v>
       </c>
       <c r="L50">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -2974,7 +2974,7 @@
         <v>21</v>
       </c>
       <c r="L51">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -3012,7 +3012,7 @@
         <v>21</v>
       </c>
       <c r="L52">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -3050,7 +3050,7 @@
         <v>21</v>
       </c>
       <c r="L53">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -3088,7 +3088,7 @@
         <v>21</v>
       </c>
       <c r="L54">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -3126,7 +3126,7 @@
         <v>21</v>
       </c>
       <c r="L55">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -3164,7 +3164,7 @@
         <v>21</v>
       </c>
       <c r="L56">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -3202,7 +3202,7 @@
         <v>21</v>
       </c>
       <c r="L57">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -3240,7 +3240,7 @@
         <v>21</v>
       </c>
       <c r="L58">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -3278,7 +3278,7 @@
         <v>21</v>
       </c>
       <c r="L59">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -3316,7 +3316,7 @@
         <v>21</v>
       </c>
       <c r="L60">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -3354,7 +3354,7 @@
         <v>21</v>
       </c>
       <c r="L61">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -3392,7 +3392,7 @@
         <v>21</v>
       </c>
       <c r="L62">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -3430,7 +3430,7 @@
         <v>21</v>
       </c>
       <c r="L63">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -3468,7 +3468,7 @@
         <v>21</v>
       </c>
       <c r="L64">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -3506,7 +3506,7 @@
         <v>21</v>
       </c>
       <c r="L65">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -3544,7 +3544,7 @@
         <v>21</v>
       </c>
       <c r="L66">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -3582,7 +3582,7 @@
         <v>21</v>
       </c>
       <c r="L67">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -3620,7 +3620,7 @@
         <v>21</v>
       </c>
       <c r="L68">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -3658,7 +3658,7 @@
         <v>21</v>
       </c>
       <c r="L69">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -3696,7 +3696,7 @@
         <v>21</v>
       </c>
       <c r="L70">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -3734,7 +3734,7 @@
         <v>21</v>
       </c>
       <c r="L71">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -3772,7 +3772,7 @@
         <v>21</v>
       </c>
       <c r="L72">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -3810,7 +3810,7 @@
         <v>21</v>
       </c>
       <c r="L73">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -3848,7 +3848,7 @@
         <v>21</v>
       </c>
       <c r="L74">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -3886,7 +3886,7 @@
         <v>21</v>
       </c>
       <c r="L75">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -3924,7 +3924,7 @@
         <v>21</v>
       </c>
       <c r="L76">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -3962,7 +3962,7 @@
         <v>21</v>
       </c>
       <c r="L77">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -4000,7 +4000,7 @@
         <v>21</v>
       </c>
       <c r="L78">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -4038,7 +4038,7 @@
         <v>21</v>
       </c>
       <c r="L79">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -4076,7 +4076,7 @@
         <v>21</v>
       </c>
       <c r="L80">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -4114,7 +4114,7 @@
         <v>21</v>
       </c>
       <c r="L81">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -4152,7 +4152,7 @@
         <v>21</v>
       </c>
       <c r="L82">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -4190,7 +4190,7 @@
         <v>21</v>
       </c>
       <c r="L83">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -4228,7 +4228,7 @@
         <v>21</v>
       </c>
       <c r="L84">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -4266,7 +4266,7 @@
         <v>21</v>
       </c>
       <c r="L85">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -4304,7 +4304,7 @@
         <v>21</v>
       </c>
       <c r="L86">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -4342,7 +4342,7 @@
         <v>21</v>
       </c>
       <c r="L87">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -4380,7 +4380,7 @@
         <v>21</v>
       </c>
       <c r="L88">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -4418,7 +4418,7 @@
         <v>21</v>
       </c>
       <c r="L89">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -4456,7 +4456,7 @@
         <v>21</v>
       </c>
       <c r="L90">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -4494,7 +4494,7 @@
         <v>21</v>
       </c>
       <c r="L91">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -4532,7 +4532,7 @@
         <v>21</v>
       </c>
       <c r="L92">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -4570,7 +4570,7 @@
         <v>21</v>
       </c>
       <c r="L93">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -4608,7 +4608,7 @@
         <v>21</v>
       </c>
       <c r="L94">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -4646,7 +4646,7 @@
         <v>21</v>
       </c>
       <c r="L95">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -4684,7 +4684,7 @@
         <v>21</v>
       </c>
       <c r="L96">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -4722,7 +4722,7 @@
         <v>21</v>
       </c>
       <c r="L97">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4760,7 +4760,7 @@
         <v>21</v>
       </c>
       <c r="L98">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -4798,7 +4798,7 @@
         <v>21</v>
       </c>
       <c r="L99">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -4836,7 +4836,7 @@
         <v>21</v>
       </c>
       <c r="L100">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4874,7 +4874,7 @@
         <v>21</v>
       </c>
       <c r="L101">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4912,7 +4912,7 @@
         <v>21</v>
       </c>
       <c r="L102">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4950,7 +4950,7 @@
         <v>21</v>
       </c>
       <c r="L103">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4988,7 +4988,7 @@
         <v>21</v>
       </c>
       <c r="L104">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -5026,7 +5026,7 @@
         <v>21</v>
       </c>
       <c r="L105">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -5064,7 +5064,7 @@
         <v>21</v>
       </c>
       <c r="L106">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -5102,7 +5102,7 @@
         <v>21</v>
       </c>
       <c r="L107">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -5140,7 +5140,7 @@
         <v>21</v>
       </c>
       <c r="L108">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -5178,7 +5178,7 @@
         <v>21</v>
       </c>
       <c r="L109">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -5216,7 +5216,7 @@
         <v>21</v>
       </c>
       <c r="L110">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -5254,7 +5254,7 @@
         <v>21</v>
       </c>
       <c r="L111">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -5349,7 +5349,7 @@
         <v>206</v>
       </c>
       <c r="L2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -5387,7 +5387,7 @@
         <v>206</v>
       </c>
       <c r="L3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -5425,7 +5425,7 @@
         <v>206</v>
       </c>
       <c r="L4">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -5463,7 +5463,7 @@
         <v>206</v>
       </c>
       <c r="L5">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -5501,7 +5501,7 @@
         <v>206</v>
       </c>
       <c r="L6">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -5539,7 +5539,7 @@
         <v>206</v>
       </c>
       <c r="L7">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -5577,7 +5577,7 @@
         <v>206</v>
       </c>
       <c r="L8">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -5615,7 +5615,7 @@
         <v>206</v>
       </c>
       <c r="L9">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -5653,7 +5653,7 @@
         <v>206</v>
       </c>
       <c r="L10">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -5691,7 +5691,7 @@
         <v>206</v>
       </c>
       <c r="L11">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/e2e-screenshots/report-round-trip/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/report-round-trip/downloaded-inventory-report.xlsx
@@ -1112,7 +1112,7 @@
         <v>21</v>
       </c>
       <c r="L2">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1150,7 +1150,7 @@
         <v>21</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1188,7 +1188,7 @@
         <v>21</v>
       </c>
       <c r="L4">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -1226,7 +1226,7 @@
         <v>21</v>
       </c>
       <c r="L5">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1264,7 +1264,7 @@
         <v>21</v>
       </c>
       <c r="L6">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1302,7 +1302,7 @@
         <v>21</v>
       </c>
       <c r="L7">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1340,7 +1340,7 @@
         <v>21</v>
       </c>
       <c r="L8">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -1378,7 +1378,7 @@
         <v>21</v>
       </c>
       <c r="L9">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1416,7 +1416,7 @@
         <v>21</v>
       </c>
       <c r="L10">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1454,7 +1454,7 @@
         <v>21</v>
       </c>
       <c r="L11">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1492,7 +1492,7 @@
         <v>21</v>
       </c>
       <c r="L12">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1530,7 +1530,7 @@
         <v>21</v>
       </c>
       <c r="L13">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1568,7 +1568,7 @@
         <v>21</v>
       </c>
       <c r="L14">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1606,7 +1606,7 @@
         <v>21</v>
       </c>
       <c r="L15">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1644,7 +1644,7 @@
         <v>21</v>
       </c>
       <c r="L16">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -1682,7 +1682,7 @@
         <v>21</v>
       </c>
       <c r="L17">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1720,7 +1720,7 @@
         <v>21</v>
       </c>
       <c r="L18">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1758,7 +1758,7 @@
         <v>21</v>
       </c>
       <c r="L19">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -1796,7 +1796,7 @@
         <v>21</v>
       </c>
       <c r="L20">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -1834,7 +1834,7 @@
         <v>21</v>
       </c>
       <c r="L21">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -1872,7 +1872,7 @@
         <v>21</v>
       </c>
       <c r="L22">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -1910,7 +1910,7 @@
         <v>21</v>
       </c>
       <c r="L23">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -1948,7 +1948,7 @@
         <v>21</v>
       </c>
       <c r="L24">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -1986,7 +1986,7 @@
         <v>21</v>
       </c>
       <c r="L25">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -2024,7 +2024,7 @@
         <v>21</v>
       </c>
       <c r="L26">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -2062,7 +2062,7 @@
         <v>21</v>
       </c>
       <c r="L27">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -2100,7 +2100,7 @@
         <v>21</v>
       </c>
       <c r="L28">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -2138,7 +2138,7 @@
         <v>21</v>
       </c>
       <c r="L29">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -2176,7 +2176,7 @@
         <v>21</v>
       </c>
       <c r="L30">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -2214,7 +2214,7 @@
         <v>21</v>
       </c>
       <c r="L31">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -2252,7 +2252,7 @@
         <v>21</v>
       </c>
       <c r="L32">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -2290,7 +2290,7 @@
         <v>21</v>
       </c>
       <c r="L33">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -2328,7 +2328,7 @@
         <v>21</v>
       </c>
       <c r="L34">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -2366,7 +2366,7 @@
         <v>21</v>
       </c>
       <c r="L35">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -2404,7 +2404,7 @@
         <v>21</v>
       </c>
       <c r="L36">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -2442,7 +2442,7 @@
         <v>21</v>
       </c>
       <c r="L37">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -2480,7 +2480,7 @@
         <v>21</v>
       </c>
       <c r="L38">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -2518,7 +2518,7 @@
         <v>21</v>
       </c>
       <c r="L39">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -2556,7 +2556,7 @@
         <v>21</v>
       </c>
       <c r="L40">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -2594,7 +2594,7 @@
         <v>21</v>
       </c>
       <c r="L41">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -2632,7 +2632,7 @@
         <v>21</v>
       </c>
       <c r="L42">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -2670,7 +2670,7 @@
         <v>21</v>
       </c>
       <c r="L43">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -2708,7 +2708,7 @@
         <v>21</v>
       </c>
       <c r="L44">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -2746,7 +2746,7 @@
         <v>21</v>
       </c>
       <c r="L45">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -2784,7 +2784,7 @@
         <v>21</v>
       </c>
       <c r="L46">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -2822,7 +2822,7 @@
         <v>21</v>
       </c>
       <c r="L47">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -2860,7 +2860,7 @@
         <v>21</v>
       </c>
       <c r="L48">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -2898,7 +2898,7 @@
         <v>21</v>
       </c>
       <c r="L49">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -2936,7 +2936,7 @@
         <v>21</v>
       </c>
       <c r="L50">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -2974,7 +2974,7 @@
         <v>21</v>
       </c>
       <c r="L51">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -3012,7 +3012,7 @@
         <v>21</v>
       </c>
       <c r="L52">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -3050,7 +3050,7 @@
         <v>21</v>
       </c>
       <c r="L53">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -3088,7 +3088,7 @@
         <v>21</v>
       </c>
       <c r="L54">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -3126,7 +3126,7 @@
         <v>21</v>
       </c>
       <c r="L55">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -3164,7 +3164,7 @@
         <v>21</v>
       </c>
       <c r="L56">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -3202,7 +3202,7 @@
         <v>21</v>
       </c>
       <c r="L57">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -3240,7 +3240,7 @@
         <v>21</v>
       </c>
       <c r="L58">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -3278,7 +3278,7 @@
         <v>21</v>
       </c>
       <c r="L59">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -3316,7 +3316,7 @@
         <v>21</v>
       </c>
       <c r="L60">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -3354,7 +3354,7 @@
         <v>21</v>
       </c>
       <c r="L61">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -3392,7 +3392,7 @@
         <v>21</v>
       </c>
       <c r="L62">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -3430,7 +3430,7 @@
         <v>21</v>
       </c>
       <c r="L63">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -3468,7 +3468,7 @@
         <v>21</v>
       </c>
       <c r="L64">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -3506,7 +3506,7 @@
         <v>21</v>
       </c>
       <c r="L65">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -3544,7 +3544,7 @@
         <v>21</v>
       </c>
       <c r="L66">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -3582,7 +3582,7 @@
         <v>21</v>
       </c>
       <c r="L67">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -3620,7 +3620,7 @@
         <v>21</v>
       </c>
       <c r="L68">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -3658,7 +3658,7 @@
         <v>21</v>
       </c>
       <c r="L69">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -3696,7 +3696,7 @@
         <v>21</v>
       </c>
       <c r="L70">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -3734,7 +3734,7 @@
         <v>21</v>
       </c>
       <c r="L71">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -3772,7 +3772,7 @@
         <v>21</v>
       </c>
       <c r="L72">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -3810,7 +3810,7 @@
         <v>21</v>
       </c>
       <c r="L73">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -3848,7 +3848,7 @@
         <v>21</v>
       </c>
       <c r="L74">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -3886,7 +3886,7 @@
         <v>21</v>
       </c>
       <c r="L75">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -3924,7 +3924,7 @@
         <v>21</v>
       </c>
       <c r="L76">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -3962,7 +3962,7 @@
         <v>21</v>
       </c>
       <c r="L77">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -4000,7 +4000,7 @@
         <v>21</v>
       </c>
       <c r="L78">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -4038,7 +4038,7 @@
         <v>21</v>
       </c>
       <c r="L79">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -4076,7 +4076,7 @@
         <v>21</v>
       </c>
       <c r="L80">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -4114,7 +4114,7 @@
         <v>21</v>
       </c>
       <c r="L81">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -4152,7 +4152,7 @@
         <v>21</v>
       </c>
       <c r="L82">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -4190,7 +4190,7 @@
         <v>21</v>
       </c>
       <c r="L83">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -4228,7 +4228,7 @@
         <v>21</v>
       </c>
       <c r="L84">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -4266,7 +4266,7 @@
         <v>21</v>
       </c>
       <c r="L85">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -4304,7 +4304,7 @@
         <v>21</v>
       </c>
       <c r="L86">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -4342,7 +4342,7 @@
         <v>21</v>
       </c>
       <c r="L87">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -4380,7 +4380,7 @@
         <v>21</v>
       </c>
       <c r="L88">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -4418,7 +4418,7 @@
         <v>21</v>
       </c>
       <c r="L89">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -4456,7 +4456,7 @@
         <v>21</v>
       </c>
       <c r="L90">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -4494,7 +4494,7 @@
         <v>21</v>
       </c>
       <c r="L91">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -4532,7 +4532,7 @@
         <v>21</v>
       </c>
       <c r="L92">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -4570,7 +4570,7 @@
         <v>21</v>
       </c>
       <c r="L93">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -4608,7 +4608,7 @@
         <v>21</v>
       </c>
       <c r="L94">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -4646,7 +4646,7 @@
         <v>21</v>
       </c>
       <c r="L95">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -4684,7 +4684,7 @@
         <v>21</v>
       </c>
       <c r="L96">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -4722,7 +4722,7 @@
         <v>21</v>
       </c>
       <c r="L97">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4760,7 +4760,7 @@
         <v>21</v>
       </c>
       <c r="L98">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -4798,7 +4798,7 @@
         <v>21</v>
       </c>
       <c r="L99">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -4836,7 +4836,7 @@
         <v>21</v>
       </c>
       <c r="L100">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4874,7 +4874,7 @@
         <v>21</v>
       </c>
       <c r="L101">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4912,7 +4912,7 @@
         <v>21</v>
       </c>
       <c r="L102">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4950,7 +4950,7 @@
         <v>21</v>
       </c>
       <c r="L103">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4988,7 +4988,7 @@
         <v>21</v>
       </c>
       <c r="L104">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -5026,7 +5026,7 @@
         <v>21</v>
       </c>
       <c r="L105">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -5064,7 +5064,7 @@
         <v>21</v>
       </c>
       <c r="L106">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -5102,7 +5102,7 @@
         <v>21</v>
       </c>
       <c r="L107">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -5140,7 +5140,7 @@
         <v>21</v>
       </c>
       <c r="L108">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -5178,7 +5178,7 @@
         <v>21</v>
       </c>
       <c r="L109">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -5216,7 +5216,7 @@
         <v>21</v>
       </c>
       <c r="L110">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -5254,7 +5254,7 @@
         <v>21</v>
       </c>
       <c r="L111">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -5349,7 +5349,7 @@
         <v>206</v>
       </c>
       <c r="L2">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -5387,7 +5387,7 @@
         <v>206</v>
       </c>
       <c r="L3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -5425,7 +5425,7 @@
         <v>206</v>
       </c>
       <c r="L4">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -5463,7 +5463,7 @@
         <v>206</v>
       </c>
       <c r="L5">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -5501,7 +5501,7 @@
         <v>206</v>
       </c>
       <c r="L6">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -5539,7 +5539,7 @@
         <v>206</v>
       </c>
       <c r="L7">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -5577,7 +5577,7 @@
         <v>206</v>
       </c>
       <c r="L8">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -5615,7 +5615,7 @@
         <v>206</v>
       </c>
       <c r="L9">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -5653,7 +5653,7 @@
         <v>206</v>
       </c>
       <c r="L10">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -5691,7 +5691,7 @@
         <v>206</v>
       </c>
       <c r="L11">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/e2e-screenshots/report-round-trip/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/report-round-trip/downloaded-inventory-report.xlsx
@@ -1112,7 +1112,7 @@
         <v>21</v>
       </c>
       <c r="L2">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1150,7 +1150,7 @@
         <v>21</v>
       </c>
       <c r="L3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1188,7 +1188,7 @@
         <v>21</v>
       </c>
       <c r="L4">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -1226,7 +1226,7 @@
         <v>21</v>
       </c>
       <c r="L5">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1264,7 +1264,7 @@
         <v>21</v>
       </c>
       <c r="L6">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1302,7 +1302,7 @@
         <v>21</v>
       </c>
       <c r="L7">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1340,7 +1340,7 @@
         <v>21</v>
       </c>
       <c r="L8">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -1378,7 +1378,7 @@
         <v>21</v>
       </c>
       <c r="L9">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1416,7 +1416,7 @@
         <v>21</v>
       </c>
       <c r="L10">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1454,7 +1454,7 @@
         <v>21</v>
       </c>
       <c r="L11">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1492,7 +1492,7 @@
         <v>21</v>
       </c>
       <c r="L12">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1530,7 +1530,7 @@
         <v>21</v>
       </c>
       <c r="L13">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1568,7 +1568,7 @@
         <v>21</v>
       </c>
       <c r="L14">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1606,7 +1606,7 @@
         <v>21</v>
       </c>
       <c r="L15">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1644,7 +1644,7 @@
         <v>21</v>
       </c>
       <c r="L16">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -1682,7 +1682,7 @@
         <v>21</v>
       </c>
       <c r="L17">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1720,7 +1720,7 @@
         <v>21</v>
       </c>
       <c r="L18">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1758,7 +1758,7 @@
         <v>21</v>
       </c>
       <c r="L19">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -1796,7 +1796,7 @@
         <v>21</v>
       </c>
       <c r="L20">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -1834,7 +1834,7 @@
         <v>21</v>
       </c>
       <c r="L21">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -1872,7 +1872,7 @@
         <v>21</v>
       </c>
       <c r="L22">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -1910,7 +1910,7 @@
         <v>21</v>
       </c>
       <c r="L23">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -1948,7 +1948,7 @@
         <v>21</v>
       </c>
       <c r="L24">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -1986,7 +1986,7 @@
         <v>21</v>
       </c>
       <c r="L25">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -2024,7 +2024,7 @@
         <v>21</v>
       </c>
       <c r="L26">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -2062,7 +2062,7 @@
         <v>21</v>
       </c>
       <c r="L27">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -2100,7 +2100,7 @@
         <v>21</v>
       </c>
       <c r="L28">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -2138,7 +2138,7 @@
         <v>21</v>
       </c>
       <c r="L29">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -2176,7 +2176,7 @@
         <v>21</v>
       </c>
       <c r="L30">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -2214,7 +2214,7 @@
         <v>21</v>
       </c>
       <c r="L31">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -2252,7 +2252,7 @@
         <v>21</v>
       </c>
       <c r="L32">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -2290,7 +2290,7 @@
         <v>21</v>
       </c>
       <c r="L33">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -2328,7 +2328,7 @@
         <v>21</v>
       </c>
       <c r="L34">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -2366,7 +2366,7 @@
         <v>21</v>
       </c>
       <c r="L35">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -2404,7 +2404,7 @@
         <v>21</v>
       </c>
       <c r="L36">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -2442,7 +2442,7 @@
         <v>21</v>
       </c>
       <c r="L37">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -2480,7 +2480,7 @@
         <v>21</v>
       </c>
       <c r="L38">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -2518,7 +2518,7 @@
         <v>21</v>
       </c>
       <c r="L39">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -2556,7 +2556,7 @@
         <v>21</v>
       </c>
       <c r="L40">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -2594,7 +2594,7 @@
         <v>21</v>
       </c>
       <c r="L41">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -2632,7 +2632,7 @@
         <v>21</v>
       </c>
       <c r="L42">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -2670,7 +2670,7 @@
         <v>21</v>
       </c>
       <c r="L43">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -2708,7 +2708,7 @@
         <v>21</v>
       </c>
       <c r="L44">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -2746,7 +2746,7 @@
         <v>21</v>
       </c>
       <c r="L45">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -2784,7 +2784,7 @@
         <v>21</v>
       </c>
       <c r="L46">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -2822,7 +2822,7 @@
         <v>21</v>
       </c>
       <c r="L47">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -2860,7 +2860,7 @@
         <v>21</v>
       </c>
       <c r="L48">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -2898,7 +2898,7 @@
         <v>21</v>
       </c>
       <c r="L49">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -2936,7 +2936,7 @@
         <v>21</v>
       </c>
       <c r="L50">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -2974,7 +2974,7 @@
         <v>21</v>
       </c>
       <c r="L51">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -3012,7 +3012,7 @@
         <v>21</v>
       </c>
       <c r="L52">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -3050,7 +3050,7 @@
         <v>21</v>
       </c>
       <c r="L53">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -3088,7 +3088,7 @@
         <v>21</v>
       </c>
       <c r="L54">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -3126,7 +3126,7 @@
         <v>21</v>
       </c>
       <c r="L55">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -3164,7 +3164,7 @@
         <v>21</v>
       </c>
       <c r="L56">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -3202,7 +3202,7 @@
         <v>21</v>
       </c>
       <c r="L57">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -3240,7 +3240,7 @@
         <v>21</v>
       </c>
       <c r="L58">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -3278,7 +3278,7 @@
         <v>21</v>
       </c>
       <c r="L59">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -3316,7 +3316,7 @@
         <v>21</v>
       </c>
       <c r="L60">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -3354,7 +3354,7 @@
         <v>21</v>
       </c>
       <c r="L61">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -3392,7 +3392,7 @@
         <v>21</v>
       </c>
       <c r="L62">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -3430,7 +3430,7 @@
         <v>21</v>
       </c>
       <c r="L63">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -3468,7 +3468,7 @@
         <v>21</v>
       </c>
       <c r="L64">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -3506,7 +3506,7 @@
         <v>21</v>
       </c>
       <c r="L65">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -3544,7 +3544,7 @@
         <v>21</v>
       </c>
       <c r="L66">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -3582,7 +3582,7 @@
         <v>21</v>
       </c>
       <c r="L67">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -3620,7 +3620,7 @@
         <v>21</v>
       </c>
       <c r="L68">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -3658,7 +3658,7 @@
         <v>21</v>
       </c>
       <c r="L69">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -3696,7 +3696,7 @@
         <v>21</v>
       </c>
       <c r="L70">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -3734,7 +3734,7 @@
         <v>21</v>
       </c>
       <c r="L71">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -3772,7 +3772,7 @@
         <v>21</v>
       </c>
       <c r="L72">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -3810,7 +3810,7 @@
         <v>21</v>
       </c>
       <c r="L73">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -3848,7 +3848,7 @@
         <v>21</v>
       </c>
       <c r="L74">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -3886,7 +3886,7 @@
         <v>21</v>
       </c>
       <c r="L75">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -3924,7 +3924,7 @@
         <v>21</v>
       </c>
       <c r="L76">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -3962,7 +3962,7 @@
         <v>21</v>
       </c>
       <c r="L77">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -4000,7 +4000,7 @@
         <v>21</v>
       </c>
       <c r="L78">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -4038,7 +4038,7 @@
         <v>21</v>
       </c>
       <c r="L79">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -4076,7 +4076,7 @@
         <v>21</v>
       </c>
       <c r="L80">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -4114,7 +4114,7 @@
         <v>21</v>
       </c>
       <c r="L81">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -4152,7 +4152,7 @@
         <v>21</v>
       </c>
       <c r="L82">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -4190,7 +4190,7 @@
         <v>21</v>
       </c>
       <c r="L83">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -4228,7 +4228,7 @@
         <v>21</v>
       </c>
       <c r="L84">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -4266,7 +4266,7 @@
         <v>21</v>
       </c>
       <c r="L85">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -4304,7 +4304,7 @@
         <v>21</v>
       </c>
       <c r="L86">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -4342,7 +4342,7 @@
         <v>21</v>
       </c>
       <c r="L87">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -4380,7 +4380,7 @@
         <v>21</v>
       </c>
       <c r="L88">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -4418,7 +4418,7 @@
         <v>21</v>
       </c>
       <c r="L89">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -4456,7 +4456,7 @@
         <v>21</v>
       </c>
       <c r="L90">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -4494,7 +4494,7 @@
         <v>21</v>
       </c>
       <c r="L91">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -4532,7 +4532,7 @@
         <v>21</v>
       </c>
       <c r="L92">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -4570,7 +4570,7 @@
         <v>21</v>
       </c>
       <c r="L93">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -4608,7 +4608,7 @@
         <v>21</v>
       </c>
       <c r="L94">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -4646,7 +4646,7 @@
         <v>21</v>
       </c>
       <c r="L95">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -4684,7 +4684,7 @@
         <v>21</v>
       </c>
       <c r="L96">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -4722,7 +4722,7 @@
         <v>21</v>
       </c>
       <c r="L97">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4760,7 +4760,7 @@
         <v>21</v>
       </c>
       <c r="L98">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -4798,7 +4798,7 @@
         <v>21</v>
       </c>
       <c r="L99">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -4836,7 +4836,7 @@
         <v>21</v>
       </c>
       <c r="L100">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4874,7 +4874,7 @@
         <v>21</v>
       </c>
       <c r="L101">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4912,7 +4912,7 @@
         <v>21</v>
       </c>
       <c r="L102">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4950,7 +4950,7 @@
         <v>21</v>
       </c>
       <c r="L103">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4988,7 +4988,7 @@
         <v>21</v>
       </c>
       <c r="L104">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -5026,7 +5026,7 @@
         <v>21</v>
       </c>
       <c r="L105">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -5064,7 +5064,7 @@
         <v>21</v>
       </c>
       <c r="L106">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -5102,7 +5102,7 @@
         <v>21</v>
       </c>
       <c r="L107">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -5140,7 +5140,7 @@
         <v>21</v>
       </c>
       <c r="L108">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -5178,7 +5178,7 @@
         <v>21</v>
       </c>
       <c r="L109">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -5216,7 +5216,7 @@
         <v>21</v>
       </c>
       <c r="L110">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -5254,7 +5254,7 @@
         <v>21</v>
       </c>
       <c r="L111">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -5349,7 +5349,7 @@
         <v>206</v>
       </c>
       <c r="L2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -5387,7 +5387,7 @@
         <v>206</v>
       </c>
       <c r="L3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -5425,7 +5425,7 @@
         <v>206</v>
       </c>
       <c r="L4">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -5463,7 +5463,7 @@
         <v>206</v>
       </c>
       <c r="L5">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -5501,7 +5501,7 @@
         <v>206</v>
       </c>
       <c r="L6">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -5539,7 +5539,7 @@
         <v>206</v>
       </c>
       <c r="L7">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -5577,7 +5577,7 @@
         <v>206</v>
       </c>
       <c r="L8">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -5615,7 +5615,7 @@
         <v>206</v>
       </c>
       <c r="L9">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -5653,7 +5653,7 @@
         <v>206</v>
       </c>
       <c r="L10">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -5691,7 +5691,7 @@
         <v>206</v>
       </c>
       <c r="L11">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/e2e-screenshots/report-round-trip/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/report-round-trip/downloaded-inventory-report.xlsx
@@ -1112,7 +1112,7 @@
         <v>21</v>
       </c>
       <c r="L2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1150,7 +1150,7 @@
         <v>21</v>
       </c>
       <c r="L3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1188,7 +1188,7 @@
         <v>21</v>
       </c>
       <c r="L4">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -1226,7 +1226,7 @@
         <v>21</v>
       </c>
       <c r="L5">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1264,7 +1264,7 @@
         <v>21</v>
       </c>
       <c r="L6">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1302,7 +1302,7 @@
         <v>21</v>
       </c>
       <c r="L7">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1340,7 +1340,7 @@
         <v>21</v>
       </c>
       <c r="L8">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -1378,7 +1378,7 @@
         <v>21</v>
       </c>
       <c r="L9">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1416,7 +1416,7 @@
         <v>21</v>
       </c>
       <c r="L10">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1454,7 +1454,7 @@
         <v>21</v>
       </c>
       <c r="L11">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1492,7 +1492,7 @@
         <v>21</v>
       </c>
       <c r="L12">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1530,7 +1530,7 @@
         <v>21</v>
       </c>
       <c r="L13">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1568,7 +1568,7 @@
         <v>21</v>
       </c>
       <c r="L14">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1606,7 +1606,7 @@
         <v>21</v>
       </c>
       <c r="L15">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1644,7 +1644,7 @@
         <v>21</v>
       </c>
       <c r="L16">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -1682,7 +1682,7 @@
         <v>21</v>
       </c>
       <c r="L17">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1720,7 +1720,7 @@
         <v>21</v>
       </c>
       <c r="L18">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1758,7 +1758,7 @@
         <v>21</v>
       </c>
       <c r="L19">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -1796,7 +1796,7 @@
         <v>21</v>
       </c>
       <c r="L20">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -1834,7 +1834,7 @@
         <v>21</v>
       </c>
       <c r="L21">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -1872,7 +1872,7 @@
         <v>21</v>
       </c>
       <c r="L22">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -1910,7 +1910,7 @@
         <v>21</v>
       </c>
       <c r="L23">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -1948,7 +1948,7 @@
         <v>21</v>
       </c>
       <c r="L24">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -1986,7 +1986,7 @@
         <v>21</v>
       </c>
       <c r="L25">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -2024,7 +2024,7 @@
         <v>21</v>
       </c>
       <c r="L26">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -2062,7 +2062,7 @@
         <v>21</v>
       </c>
       <c r="L27">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -2100,7 +2100,7 @@
         <v>21</v>
       </c>
       <c r="L28">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -2138,7 +2138,7 @@
         <v>21</v>
       </c>
       <c r="L29">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -2176,7 +2176,7 @@
         <v>21</v>
       </c>
       <c r="L30">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -2214,7 +2214,7 @@
         <v>21</v>
       </c>
       <c r="L31">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -2252,7 +2252,7 @@
         <v>21</v>
       </c>
       <c r="L32">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -2290,7 +2290,7 @@
         <v>21</v>
       </c>
       <c r="L33">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -2328,7 +2328,7 @@
         <v>21</v>
       </c>
       <c r="L34">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -2366,7 +2366,7 @@
         <v>21</v>
       </c>
       <c r="L35">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -2404,7 +2404,7 @@
         <v>21</v>
       </c>
       <c r="L36">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -2442,7 +2442,7 @@
         <v>21</v>
       </c>
       <c r="L37">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -2480,7 +2480,7 @@
         <v>21</v>
       </c>
       <c r="L38">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -2518,7 +2518,7 @@
         <v>21</v>
       </c>
       <c r="L39">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -2556,7 +2556,7 @@
         <v>21</v>
       </c>
       <c r="L40">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -2594,7 +2594,7 @@
         <v>21</v>
       </c>
       <c r="L41">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -2632,7 +2632,7 @@
         <v>21</v>
       </c>
       <c r="L42">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -2670,7 +2670,7 @@
         <v>21</v>
       </c>
       <c r="L43">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -2708,7 +2708,7 @@
         <v>21</v>
       </c>
       <c r="L44">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -2746,7 +2746,7 @@
         <v>21</v>
       </c>
       <c r="L45">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -2784,7 +2784,7 @@
         <v>21</v>
       </c>
       <c r="L46">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -2822,7 +2822,7 @@
         <v>21</v>
       </c>
       <c r="L47">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -2860,7 +2860,7 @@
         <v>21</v>
       </c>
       <c r="L48">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -2898,7 +2898,7 @@
         <v>21</v>
       </c>
       <c r="L49">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -2936,7 +2936,7 @@
         <v>21</v>
       </c>
       <c r="L50">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -2974,7 +2974,7 @@
         <v>21</v>
       </c>
       <c r="L51">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -3012,7 +3012,7 @@
         <v>21</v>
       </c>
       <c r="L52">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -3050,7 +3050,7 @@
         <v>21</v>
       </c>
       <c r="L53">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -3088,7 +3088,7 @@
         <v>21</v>
       </c>
       <c r="L54">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -3126,7 +3126,7 @@
         <v>21</v>
       </c>
       <c r="L55">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -3164,7 +3164,7 @@
         <v>21</v>
       </c>
       <c r="L56">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -3202,7 +3202,7 @@
         <v>21</v>
       </c>
       <c r="L57">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -3240,7 +3240,7 @@
         <v>21</v>
       </c>
       <c r="L58">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -3278,7 +3278,7 @@
         <v>21</v>
       </c>
       <c r="L59">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -3316,7 +3316,7 @@
         <v>21</v>
       </c>
       <c r="L60">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -3354,7 +3354,7 @@
         <v>21</v>
       </c>
       <c r="L61">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -3392,7 +3392,7 @@
         <v>21</v>
       </c>
       <c r="L62">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -3430,7 +3430,7 @@
         <v>21</v>
       </c>
       <c r="L63">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -3468,7 +3468,7 @@
         <v>21</v>
       </c>
       <c r="L64">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -3506,7 +3506,7 @@
         <v>21</v>
       </c>
       <c r="L65">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -3544,7 +3544,7 @@
         <v>21</v>
       </c>
       <c r="L66">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -3582,7 +3582,7 @@
         <v>21</v>
       </c>
       <c r="L67">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -3620,7 +3620,7 @@
         <v>21</v>
       </c>
       <c r="L68">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -3658,7 +3658,7 @@
         <v>21</v>
       </c>
       <c r="L69">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -3696,7 +3696,7 @@
         <v>21</v>
       </c>
       <c r="L70">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -3734,7 +3734,7 @@
         <v>21</v>
       </c>
       <c r="L71">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -3772,7 +3772,7 @@
         <v>21</v>
       </c>
       <c r="L72">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -3810,7 +3810,7 @@
         <v>21</v>
       </c>
       <c r="L73">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -3848,7 +3848,7 @@
         <v>21</v>
       </c>
       <c r="L74">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -3886,7 +3886,7 @@
         <v>21</v>
       </c>
       <c r="L75">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -3924,7 +3924,7 @@
         <v>21</v>
       </c>
       <c r="L76">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -3962,7 +3962,7 @@
         <v>21</v>
       </c>
       <c r="L77">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -4000,7 +4000,7 @@
         <v>21</v>
       </c>
       <c r="L78">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -4038,7 +4038,7 @@
         <v>21</v>
       </c>
       <c r="L79">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -4076,7 +4076,7 @@
         <v>21</v>
       </c>
       <c r="L80">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -4114,7 +4114,7 @@
         <v>21</v>
       </c>
       <c r="L81">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -4152,7 +4152,7 @@
         <v>21</v>
       </c>
       <c r="L82">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -4190,7 +4190,7 @@
         <v>21</v>
       </c>
       <c r="L83">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -4228,7 +4228,7 @@
         <v>21</v>
       </c>
       <c r="L84">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -4266,7 +4266,7 @@
         <v>21</v>
       </c>
       <c r="L85">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -4304,7 +4304,7 @@
         <v>21</v>
       </c>
       <c r="L86">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -4342,7 +4342,7 @@
         <v>21</v>
       </c>
       <c r="L87">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -4380,7 +4380,7 @@
         <v>21</v>
       </c>
       <c r="L88">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -4418,7 +4418,7 @@
         <v>21</v>
       </c>
       <c r="L89">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -4456,7 +4456,7 @@
         <v>21</v>
       </c>
       <c r="L90">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -4494,7 +4494,7 @@
         <v>21</v>
       </c>
       <c r="L91">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -4532,7 +4532,7 @@
         <v>21</v>
       </c>
       <c r="L92">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -4570,7 +4570,7 @@
         <v>21</v>
       </c>
       <c r="L93">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -4608,7 +4608,7 @@
         <v>21</v>
       </c>
       <c r="L94">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -4646,7 +4646,7 @@
         <v>21</v>
       </c>
       <c r="L95">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -4684,7 +4684,7 @@
         <v>21</v>
       </c>
       <c r="L96">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -4722,7 +4722,7 @@
         <v>21</v>
       </c>
       <c r="L97">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4760,7 +4760,7 @@
         <v>21</v>
       </c>
       <c r="L98">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -4798,7 +4798,7 @@
         <v>21</v>
       </c>
       <c r="L99">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -4836,7 +4836,7 @@
         <v>21</v>
       </c>
       <c r="L100">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4874,7 +4874,7 @@
         <v>21</v>
       </c>
       <c r="L101">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4912,7 +4912,7 @@
         <v>21</v>
       </c>
       <c r="L102">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4950,7 +4950,7 @@
         <v>21</v>
       </c>
       <c r="L103">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4988,7 +4988,7 @@
         <v>21</v>
       </c>
       <c r="L104">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -5026,7 +5026,7 @@
         <v>21</v>
       </c>
       <c r="L105">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -5064,7 +5064,7 @@
         <v>21</v>
       </c>
       <c r="L106">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -5102,7 +5102,7 @@
         <v>21</v>
       </c>
       <c r="L107">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -5140,7 +5140,7 @@
         <v>21</v>
       </c>
       <c r="L108">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -5178,7 +5178,7 @@
         <v>21</v>
       </c>
       <c r="L109">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -5216,7 +5216,7 @@
         <v>21</v>
       </c>
       <c r="L110">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -5254,7 +5254,7 @@
         <v>21</v>
       </c>
       <c r="L111">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -5349,7 +5349,7 @@
         <v>206</v>
       </c>
       <c r="L2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -5387,7 +5387,7 @@
         <v>206</v>
       </c>
       <c r="L3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -5425,7 +5425,7 @@
         <v>206</v>
       </c>
       <c r="L4">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -5463,7 +5463,7 @@
         <v>206</v>
       </c>
       <c r="L5">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -5501,7 +5501,7 @@
         <v>206</v>
       </c>
       <c r="L6">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -5539,7 +5539,7 @@
         <v>206</v>
       </c>
       <c r="L7">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -5577,7 +5577,7 @@
         <v>206</v>
       </c>
       <c r="L8">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -5615,7 +5615,7 @@
         <v>206</v>
       </c>
       <c r="L9">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -5653,7 +5653,7 @@
         <v>206</v>
       </c>
       <c r="L10">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -5691,7 +5691,7 @@
         <v>206</v>
       </c>
       <c r="L11">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/e2e-screenshots/report-round-trip/downloaded-inventory-report.xlsx
+++ b/e2e-screenshots/report-round-trip/downloaded-inventory-report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="208">
   <si>
     <t>Stock In Date</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t>Age (days)</t>
+  </si>
+  <si>
+    <t>Return Date</t>
   </si>
   <si>
     <t>2026-07-20</t>
@@ -1029,17 +1032,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="30" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="12" max="13" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1076,4189 +1079,4522 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2">
         <v>232.81</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2">
+        <v>51</v>
+      </c>
+      <c r="M2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I3">
         <v>517.1</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L3">
+        <v>51</v>
+      </c>
+      <c r="M3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" t="s">
-        <v>18</v>
-      </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4">
         <v>327.58</v>
       </c>
       <c r="J4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="M4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" t="s">
         <v>32</v>
-      </c>
-      <c r="B5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" t="s">
-        <v>31</v>
       </c>
       <c r="I5">
         <v>256.93</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L5">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="M5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
         <v>37</v>
       </c>
-      <c r="D6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" t="s">
-        <v>36</v>
-      </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I6">
         <v>223.04</v>
       </c>
       <c r="J6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L6">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="M6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I7">
         <v>453.75</v>
       </c>
       <c r="J7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L7">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="M7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8">
         <v>237.5</v>
       </c>
       <c r="J8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L8">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="M8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" t="s">
         <v>46</v>
-      </c>
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" t="s">
-        <v>45</v>
       </c>
       <c r="I9">
         <v>293.74</v>
       </c>
       <c r="J9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L9">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="M9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I10">
         <v>484.06</v>
       </c>
       <c r="J10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L10">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="M10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I11">
         <v>417.16</v>
       </c>
       <c r="J11" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11">
+        <v>56</v>
+      </c>
+      <c r="M11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" t="s">
         <v>20</v>
-      </c>
-      <c r="K11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" t="s">
-        <v>59</v>
-      </c>
-      <c r="H12" t="s">
-        <v>19</v>
       </c>
       <c r="I12">
         <v>500.85</v>
       </c>
       <c r="J12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12">
+        <v>57</v>
+      </c>
+      <c r="M12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" t="s">
         <v>20</v>
-      </c>
-      <c r="K12" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13" t="s">
-        <v>49</v>
-      </c>
-      <c r="H13" t="s">
-        <v>19</v>
       </c>
       <c r="I13">
         <v>242</v>
       </c>
       <c r="J13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13">
+        <v>57</v>
+      </c>
+      <c r="M13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" t="s">
         <v>20</v>
-      </c>
-      <c r="K13" t="s">
-        <v>21</v>
-      </c>
-      <c r="L13">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>61</v>
-      </c>
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" t="s">
-        <v>63</v>
-      </c>
-      <c r="H14" t="s">
-        <v>19</v>
       </c>
       <c r="I14">
         <v>334.64</v>
       </c>
       <c r="J14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L14">
+        <v>58</v>
+      </c>
+      <c r="M14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" t="s">
-        <v>25</v>
-      </c>
       <c r="F15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I15">
         <v>462.92</v>
       </c>
       <c r="J15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L15">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+      <c r="M15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I16">
         <v>232.24</v>
       </c>
       <c r="J16" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" t="s">
+        <v>22</v>
+      </c>
+      <c r="L16">
+        <v>59</v>
+      </c>
+      <c r="M16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" t="s">
+        <v>56</v>
+      </c>
+      <c r="G17" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" t="s">
         <v>20</v>
-      </c>
-      <c r="K16" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" t="s">
-        <v>42</v>
-      </c>
-      <c r="E17" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" t="s">
-        <v>19</v>
       </c>
       <c r="I17">
         <v>530.25</v>
       </c>
       <c r="J17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L17">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="M17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I18">
         <v>192.93</v>
       </c>
       <c r="J18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L18">
+        <v>60</v>
+      </c>
+      <c r="M18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" t="s">
+        <v>37</v>
+      </c>
+      <c r="H19" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>68</v>
-      </c>
-      <c r="B19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" t="s">
-        <v>42</v>
-      </c>
-      <c r="E19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" t="s">
-        <v>43</v>
-      </c>
-      <c r="G19" t="s">
-        <v>36</v>
-      </c>
-      <c r="H19" t="s">
-        <v>27</v>
       </c>
       <c r="I19">
         <v>335.04</v>
       </c>
       <c r="J19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L19">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="M19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I20">
         <v>268.59</v>
       </c>
       <c r="J20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L20">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="M20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I21">
         <v>227.85</v>
       </c>
       <c r="J21" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" t="s">
+        <v>22</v>
+      </c>
+      <c r="L21">
+        <v>61</v>
+      </c>
+      <c r="M21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>50</v>
+      </c>
+      <c r="H22" t="s">
         <v>20</v>
-      </c>
-      <c r="K21" t="s">
-        <v>21</v>
-      </c>
-      <c r="L21">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>75</v>
-      </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" t="s">
-        <v>49</v>
-      </c>
-      <c r="H22" t="s">
-        <v>19</v>
       </c>
       <c r="I22">
         <v>422.16</v>
       </c>
       <c r="J22" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" t="s">
+        <v>22</v>
+      </c>
+      <c r="L22">
+        <v>62</v>
+      </c>
+      <c r="M22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" t="s">
+        <v>71</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>60</v>
+      </c>
+      <c r="H23" t="s">
         <v>20</v>
-      </c>
-      <c r="K22" t="s">
-        <v>21</v>
-      </c>
-      <c r="L22">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>75</v>
-      </c>
-      <c r="B23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" t="s">
-        <v>42</v>
-      </c>
-      <c r="E23" t="s">
-        <v>70</v>
-      </c>
-      <c r="F23" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" t="s">
-        <v>59</v>
-      </c>
-      <c r="H23" t="s">
-        <v>19</v>
       </c>
       <c r="I23">
         <v>186.57</v>
       </c>
       <c r="J23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L23">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="M23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I24">
         <v>262.94</v>
       </c>
       <c r="J24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L24">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="M24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I25">
         <v>275.49</v>
       </c>
       <c r="J25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L25">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="M25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I26">
         <v>413.46</v>
       </c>
       <c r="J26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L26">
+        <v>64</v>
+      </c>
+      <c r="M26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>81</v>
+      </c>
+      <c r="H27" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" t="s">
-        <v>85</v>
-      </c>
-      <c r="D27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" t="s">
-        <v>17</v>
-      </c>
-      <c r="G27" t="s">
-        <v>80</v>
-      </c>
-      <c r="H27" t="s">
-        <v>31</v>
       </c>
       <c r="I27">
         <v>495.98</v>
       </c>
       <c r="J27" t="s">
+        <v>21</v>
+      </c>
+      <c r="K27" t="s">
+        <v>22</v>
+      </c>
+      <c r="L27">
+        <v>65</v>
+      </c>
+      <c r="M27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>37</v>
+      </c>
+      <c r="H28" t="s">
         <v>20</v>
-      </c>
-      <c r="K27" t="s">
-        <v>21</v>
-      </c>
-      <c r="L27">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>84</v>
-      </c>
-      <c r="B28" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" t="s">
-        <v>86</v>
-      </c>
-      <c r="D28" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" t="s">
-        <v>16</v>
-      </c>
-      <c r="F28" t="s">
-        <v>17</v>
-      </c>
-      <c r="G28" t="s">
-        <v>36</v>
-      </c>
-      <c r="H28" t="s">
-        <v>19</v>
       </c>
       <c r="I28">
         <v>246.21</v>
       </c>
       <c r="J28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L28">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="M28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I29">
         <v>305.4</v>
       </c>
       <c r="J29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L29">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="M29" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I30">
         <v>209.59</v>
       </c>
       <c r="J30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L30">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="M30" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I31">
         <v>511.35</v>
       </c>
       <c r="J31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L31">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="M31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I32">
         <v>196.32</v>
       </c>
       <c r="J32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L32">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+      <c r="M32" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I33">
         <v>315.22</v>
       </c>
       <c r="J33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K33" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L33">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+      <c r="M33" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G34" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I34">
         <v>290.37</v>
       </c>
       <c r="J34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L34">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="M34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I35">
         <v>231.07</v>
       </c>
       <c r="J35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L35">
+        <v>69</v>
+      </c>
+      <c r="M35" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" t="s">
+        <v>100</v>
+      </c>
+      <c r="D36" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" t="s">
+        <v>26</v>
+      </c>
+      <c r="F36" t="s">
+        <v>56</v>
+      </c>
+      <c r="G36" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>98</v>
-      </c>
-      <c r="B36" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36" t="s">
-        <v>99</v>
-      </c>
-      <c r="D36" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" t="s">
-        <v>25</v>
-      </c>
-      <c r="F36" t="s">
-        <v>55</v>
-      </c>
-      <c r="G36" t="s">
-        <v>36</v>
-      </c>
       <c r="H36" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I36">
         <v>418.34</v>
       </c>
       <c r="J36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L36">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="M36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D37" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F37" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H37" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I37">
         <v>190.34</v>
       </c>
       <c r="J37" t="s">
+        <v>21</v>
+      </c>
+      <c r="K37" t="s">
+        <v>22</v>
+      </c>
+      <c r="L37">
+        <v>70</v>
+      </c>
+      <c r="M37" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" t="s">
+        <v>103</v>
+      </c>
+      <c r="D38" t="s">
+        <v>43</v>
+      </c>
+      <c r="E38" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" t="s">
+        <v>56</v>
+      </c>
+      <c r="G38" t="s">
+        <v>64</v>
+      </c>
+      <c r="H38" t="s">
         <v>20</v>
-      </c>
-      <c r="K37" t="s">
-        <v>21</v>
-      </c>
-      <c r="L37">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>101</v>
-      </c>
-      <c r="B38" t="s">
-        <v>47</v>
-      </c>
-      <c r="C38" t="s">
-        <v>102</v>
-      </c>
-      <c r="D38" t="s">
-        <v>42</v>
-      </c>
-      <c r="E38" t="s">
-        <v>16</v>
-      </c>
-      <c r="F38" t="s">
-        <v>55</v>
-      </c>
-      <c r="G38" t="s">
-        <v>63</v>
-      </c>
-      <c r="H38" t="s">
-        <v>19</v>
       </c>
       <c r="I38">
         <v>253.86</v>
       </c>
       <c r="J38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L38">
+        <v>71</v>
+      </c>
+      <c r="M38" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" t="s">
+        <v>104</v>
+      </c>
+      <c r="D39" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>101</v>
-      </c>
-      <c r="B39" t="s">
-        <v>33</v>
-      </c>
-      <c r="C39" t="s">
-        <v>103</v>
-      </c>
-      <c r="D39" t="s">
-        <v>38</v>
-      </c>
       <c r="E39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G39" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H39" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I39">
         <v>262.14</v>
       </c>
       <c r="J39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L39">
+        <v>71</v>
+      </c>
+      <c r="M39" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>105</v>
+      </c>
+      <c r="B40" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" t="s">
+        <v>106</v>
+      </c>
+      <c r="D40" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>104</v>
-      </c>
-      <c r="B40" t="s">
-        <v>53</v>
-      </c>
-      <c r="C40" t="s">
-        <v>105</v>
-      </c>
-      <c r="D40" t="s">
-        <v>38</v>
-      </c>
       <c r="E40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F40" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G40" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I40">
         <v>499.6</v>
       </c>
       <c r="J40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L40">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="M40" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C41" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D41" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E41" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I41">
         <v>422.7</v>
       </c>
       <c r="J41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L41">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="M41" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B42" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C42" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D42" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E42" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G42" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I42">
         <v>499.91</v>
       </c>
       <c r="J42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L42">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="M42" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C43" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D43" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E43" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I43">
         <v>257.31</v>
       </c>
       <c r="J43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K43" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L43">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="M43" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B44" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C44" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D44" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E44" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G44" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I44">
         <v>325.88</v>
       </c>
       <c r="J44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L44">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+      <c r="M44" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C45" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D45" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F45" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G45" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H45" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I45">
         <v>476.5</v>
       </c>
       <c r="J45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K45" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L45">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+      <c r="M45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C46" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G46" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I46">
         <v>233.36</v>
       </c>
       <c r="J46" t="s">
+        <v>21</v>
+      </c>
+      <c r="K46" t="s">
+        <v>22</v>
+      </c>
+      <c r="L46">
+        <v>75</v>
+      </c>
+      <c r="M46" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>114</v>
+      </c>
+      <c r="B47" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" t="s">
+        <v>116</v>
+      </c>
+      <c r="D47" t="s">
+        <v>36</v>
+      </c>
+      <c r="E47" t="s">
+        <v>26</v>
+      </c>
+      <c r="F47" t="s">
+        <v>44</v>
+      </c>
+      <c r="G47" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" t="s">
         <v>20</v>
-      </c>
-      <c r="K46" t="s">
-        <v>21</v>
-      </c>
-      <c r="L46">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>113</v>
-      </c>
-      <c r="B47" t="s">
-        <v>22</v>
-      </c>
-      <c r="C47" t="s">
-        <v>115</v>
-      </c>
-      <c r="D47" t="s">
-        <v>35</v>
-      </c>
-      <c r="E47" t="s">
-        <v>25</v>
-      </c>
-      <c r="F47" t="s">
-        <v>43</v>
-      </c>
-      <c r="G47" t="s">
-        <v>18</v>
-      </c>
-      <c r="H47" t="s">
-        <v>19</v>
       </c>
       <c r="I47">
         <v>501.14</v>
       </c>
       <c r="J47" t="s">
+        <v>21</v>
+      </c>
+      <c r="K47" t="s">
+        <v>22</v>
+      </c>
+      <c r="L47">
+        <v>75</v>
+      </c>
+      <c r="M47" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>117</v>
+      </c>
+      <c r="B48" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48" t="s">
+        <v>118</v>
+      </c>
+      <c r="D48" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>45</v>
+      </c>
+      <c r="H48" t="s">
         <v>20</v>
-      </c>
-      <c r="K47" t="s">
-        <v>21</v>
-      </c>
-      <c r="L47">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>116</v>
-      </c>
-      <c r="B48" t="s">
-        <v>29</v>
-      </c>
-      <c r="C48" t="s">
-        <v>117</v>
-      </c>
-      <c r="D48" t="s">
-        <v>24</v>
-      </c>
-      <c r="E48" t="s">
-        <v>16</v>
-      </c>
-      <c r="F48" t="s">
-        <v>17</v>
-      </c>
-      <c r="G48" t="s">
-        <v>44</v>
-      </c>
-      <c r="H48" t="s">
-        <v>19</v>
       </c>
       <c r="I48">
         <v>334.66</v>
       </c>
       <c r="J48" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K48" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L48">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="M48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B49" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C49" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D49" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F49" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G49" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H49" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I49">
         <v>276.86</v>
       </c>
       <c r="J49" t="s">
+        <v>21</v>
+      </c>
+      <c r="K49" t="s">
+        <v>22</v>
+      </c>
+      <c r="L49">
+        <v>77</v>
+      </c>
+      <c r="M49" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>119</v>
+      </c>
+      <c r="B50" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" t="s">
+        <v>121</v>
+      </c>
+      <c r="D50" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" t="s">
+        <v>27</v>
+      </c>
+      <c r="G50" t="s">
+        <v>50</v>
+      </c>
+      <c r="H50" t="s">
         <v>20</v>
-      </c>
-      <c r="K49" t="s">
-        <v>21</v>
-      </c>
-      <c r="L49">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>118</v>
-      </c>
-      <c r="B50" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" t="s">
-        <v>120</v>
-      </c>
-      <c r="D50" t="s">
-        <v>24</v>
-      </c>
-      <c r="E50" t="s">
-        <v>16</v>
-      </c>
-      <c r="F50" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" t="s">
-        <v>49</v>
-      </c>
-      <c r="H50" t="s">
-        <v>19</v>
       </c>
       <c r="I50">
         <v>222.91</v>
       </c>
       <c r="J50" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K50" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L50">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="M50" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B51" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C51" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D51" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E51" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G51" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H51" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I51">
         <v>449.53</v>
       </c>
       <c r="J51" t="s">
+        <v>21</v>
+      </c>
+      <c r="K51" t="s">
+        <v>22</v>
+      </c>
+      <c r="L51">
+        <v>78</v>
+      </c>
+      <c r="M51" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>124</v>
+      </c>
+      <c r="B52" t="s">
+        <v>48</v>
+      </c>
+      <c r="C52" t="s">
+        <v>125</v>
+      </c>
+      <c r="D52" t="s">
+        <v>43</v>
+      </c>
+      <c r="E52" t="s">
+        <v>17</v>
+      </c>
+      <c r="F52" t="s">
+        <v>56</v>
+      </c>
+      <c r="G52" t="s">
+        <v>52</v>
+      </c>
+      <c r="H52" t="s">
         <v>20</v>
-      </c>
-      <c r="K51" t="s">
-        <v>21</v>
-      </c>
-      <c r="L51">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>123</v>
-      </c>
-      <c r="B52" t="s">
-        <v>47</v>
-      </c>
-      <c r="C52" t="s">
-        <v>124</v>
-      </c>
-      <c r="D52" t="s">
-        <v>42</v>
-      </c>
-      <c r="E52" t="s">
-        <v>16</v>
-      </c>
-      <c r="F52" t="s">
-        <v>55</v>
-      </c>
-      <c r="G52" t="s">
-        <v>51</v>
-      </c>
-      <c r="H52" t="s">
-        <v>19</v>
       </c>
       <c r="I52">
         <v>246.31</v>
       </c>
       <c r="J52" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K52" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L52">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="M52" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C53" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D53" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E53" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F53" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G53" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H53" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I53">
         <v>264.82</v>
       </c>
       <c r="J53" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K53" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L53">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="M53" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B54" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C54" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D54" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E54" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F54" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G54" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I54">
         <v>469.17</v>
       </c>
       <c r="J54" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K54" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L54">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="M54" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B55" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C55" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D55" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E55" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F55" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G55" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H55" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I55">
         <v>451.39</v>
       </c>
       <c r="J55" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K55" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L55">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="M55" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B56" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C56" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D56" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E56" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F56" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G56" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H56" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I56">
         <v>529.23</v>
       </c>
       <c r="J56" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K56" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L56">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+      <c r="M56" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B57" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C57" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D57" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E57" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F57" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G57" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H57" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I57">
         <v>263.11</v>
       </c>
       <c r="J57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K57" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L57">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+      <c r="M57" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B58" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C58" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D58" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E58" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F58" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G58" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H58" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I58">
         <v>291.51</v>
       </c>
       <c r="J58" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K58" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L58">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+      <c r="M58" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B59" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C59" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D59" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E59" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F59" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G59" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H59" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I59">
         <v>316.37</v>
       </c>
       <c r="J59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K59" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L59">
+        <v>82</v>
+      </c>
+      <c r="M59" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>134</v>
+      </c>
+      <c r="B60" t="s">
+        <v>54</v>
+      </c>
+      <c r="C60" t="s">
+        <v>136</v>
+      </c>
+      <c r="D60" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" t="s">
+        <v>26</v>
+      </c>
+      <c r="F60" t="s">
+        <v>56</v>
+      </c>
+      <c r="G60" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>133</v>
-      </c>
-      <c r="B60" t="s">
-        <v>53</v>
-      </c>
-      <c r="C60" t="s">
-        <v>135</v>
-      </c>
-      <c r="D60" t="s">
-        <v>24</v>
-      </c>
-      <c r="E60" t="s">
-        <v>25</v>
-      </c>
-      <c r="F60" t="s">
-        <v>55</v>
-      </c>
-      <c r="G60" t="s">
-        <v>49</v>
-      </c>
       <c r="H60" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I60">
         <v>482.51</v>
       </c>
       <c r="J60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K60" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L60">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="M60" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B61" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C61" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D61" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F61" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G61" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H61" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I61">
         <v>454.29</v>
       </c>
       <c r="J61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K61" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L61">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="M61" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B62" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C62" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D62" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E62" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F62" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G62" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H62" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I62">
         <v>219.35</v>
       </c>
       <c r="J62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K62" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L62">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="M62" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B63" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C63" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D63" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E63" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F63" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G63" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H63" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I63">
         <v>500.16</v>
       </c>
       <c r="J63" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K63" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L63">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="M63" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C64" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D64" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E64" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F64" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G64" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H64" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I64">
         <v>244.68</v>
       </c>
       <c r="J64" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K64" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L64">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="M64" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C65" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D65" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E65" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F65" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G65" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H65" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I65">
         <v>212.15</v>
       </c>
       <c r="J65" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K65" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L65">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="M65" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B66" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C66" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D66" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E66" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F66" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G66" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H66" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I66">
         <v>337.53</v>
       </c>
       <c r="J66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K66" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L66">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="M66" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B67" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C67" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D67" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E67" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F67" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G67" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H67" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I67">
         <v>495.44</v>
       </c>
       <c r="J67" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K67" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L67">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="M67" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B68" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D68" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E68" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F68" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G68" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H68" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I68">
         <v>280.37</v>
       </c>
       <c r="J68" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K68" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L68">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="M68" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B69" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C69" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D69" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E69" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F69" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G69" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H69" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I69">
         <v>222.24</v>
       </c>
       <c r="J69" t="s">
+        <v>21</v>
+      </c>
+      <c r="K69" t="s">
+        <v>22</v>
+      </c>
+      <c r="L69">
+        <v>85</v>
+      </c>
+      <c r="M69" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>146</v>
+      </c>
+      <c r="B70" t="s">
+        <v>23</v>
+      </c>
+      <c r="C70" t="s">
+        <v>149</v>
+      </c>
+      <c r="D70" t="s">
+        <v>39</v>
+      </c>
+      <c r="E70" t="s">
+        <v>26</v>
+      </c>
+      <c r="F70" t="s">
+        <v>56</v>
+      </c>
+      <c r="G70" t="s">
+        <v>37</v>
+      </c>
+      <c r="H70" t="s">
         <v>20</v>
-      </c>
-      <c r="K69" t="s">
-        <v>21</v>
-      </c>
-      <c r="L69">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>145</v>
-      </c>
-      <c r="B70" t="s">
-        <v>22</v>
-      </c>
-      <c r="C70" t="s">
-        <v>148</v>
-      </c>
-      <c r="D70" t="s">
-        <v>38</v>
-      </c>
-      <c r="E70" t="s">
-        <v>25</v>
-      </c>
-      <c r="F70" t="s">
-        <v>55</v>
-      </c>
-      <c r="G70" t="s">
-        <v>36</v>
-      </c>
-      <c r="H70" t="s">
-        <v>19</v>
       </c>
       <c r="I70">
         <v>513.75</v>
       </c>
       <c r="J70" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K70" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L70">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="M70" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B71" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C71" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D71" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E71" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F71" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G71" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H71" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I71">
         <v>450.57</v>
       </c>
       <c r="J71" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K71" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L71">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+      <c r="M71" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C72" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D72" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E72" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F72" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G72" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I72">
         <v>197.28</v>
       </c>
       <c r="J72" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K72" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L72">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+      <c r="M72" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B73" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C73" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D73" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E73" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F73" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G73" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I73">
         <v>334.98</v>
       </c>
       <c r="J73" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K73" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L73">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+      <c r="M73" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B74" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C74" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D74" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E74" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F74" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G74" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H74" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I74">
         <v>230.57</v>
       </c>
       <c r="J74" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K74" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L74">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+      <c r="M74" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B75" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C75" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D75" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E75" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F75" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G75" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H75" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I75">
         <v>287.02</v>
       </c>
       <c r="J75" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K75" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L75">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+      <c r="M75" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B76" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C76" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D76" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E76" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F76" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G76" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H76" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I76">
         <v>234.05</v>
       </c>
       <c r="J76" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K76" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L76">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+      <c r="M76" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B77" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C77" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D77" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E77" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F77" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G77" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H77" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I77">
         <v>431.55</v>
       </c>
       <c r="J77" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K77" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L77">
+        <v>88</v>
+      </c>
+      <c r="M77" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>158</v>
+      </c>
+      <c r="B78" t="s">
+        <v>14</v>
+      </c>
+      <c r="C78" t="s">
+        <v>160</v>
+      </c>
+      <c r="D78" t="s">
+        <v>43</v>
+      </c>
+      <c r="E78" t="s">
+        <v>71</v>
+      </c>
+      <c r="F78" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>157</v>
-      </c>
-      <c r="B78" t="s">
-        <v>13</v>
-      </c>
-      <c r="C78" t="s">
-        <v>159</v>
-      </c>
-      <c r="D78" t="s">
-        <v>42</v>
-      </c>
-      <c r="E78" t="s">
-        <v>70</v>
-      </c>
-      <c r="F78" t="s">
-        <v>55</v>
-      </c>
       <c r="G78" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H78" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I78">
         <v>212.63</v>
       </c>
       <c r="J78" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K78" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L78">
+        <v>88</v>
+      </c>
+      <c r="M78" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>161</v>
+      </c>
+      <c r="B79" t="s">
+        <v>23</v>
+      </c>
+      <c r="C79" t="s">
+        <v>162</v>
+      </c>
+      <c r="D79" t="s">
+        <v>43</v>
+      </c>
+      <c r="E79" t="s">
+        <v>26</v>
+      </c>
+      <c r="F79" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>160</v>
-      </c>
-      <c r="B79" t="s">
-        <v>22</v>
-      </c>
-      <c r="C79" t="s">
-        <v>161</v>
-      </c>
-      <c r="D79" t="s">
-        <v>42</v>
-      </c>
-      <c r="E79" t="s">
-        <v>25</v>
-      </c>
-      <c r="F79" t="s">
-        <v>55</v>
-      </c>
       <c r="G79" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H79" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I79">
         <v>514.23</v>
       </c>
       <c r="J79" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K79" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L79">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="M79" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B80" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C80" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D80" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E80" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F80" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G80" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H80" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I80">
         <v>250.16</v>
       </c>
       <c r="J80" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K80" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L80">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="M80" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B81" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C81" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D81" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E81" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F81" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G81" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H81" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I81">
         <v>276.06</v>
       </c>
       <c r="J81" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K81" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L81">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="M81" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B82" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C82" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D82" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E82" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F82" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G82" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I82">
         <v>311.8</v>
       </c>
       <c r="J82" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K82" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L82">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="M82" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B83" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C83" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D83" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E83" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F83" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G83" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H83" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I83">
         <v>430.1</v>
       </c>
       <c r="J83" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K83" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L83">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="M83" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B84" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C84" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D84" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E84" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F84" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G84" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H84" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I84">
         <v>229.85</v>
       </c>
       <c r="J84" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K84" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L84">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+      <c r="M84" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B85" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C85" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D85" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E85" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F85" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G85" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H85" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I85">
         <v>507.95</v>
       </c>
       <c r="J85" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K85" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L85">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+      <c r="M85" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B86" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C86" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D86" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E86" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F86" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G86" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H86" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I86">
         <v>255.03</v>
       </c>
       <c r="J86" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K86" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L86">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+      <c r="M86" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B87" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C87" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D87" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E87" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F87" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G87" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H87" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I87">
         <v>196.74</v>
       </c>
       <c r="J87" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K87" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L87">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+      <c r="M87" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B88" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C88" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D88" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E88" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F88" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G88" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H88" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I88">
         <v>336.42</v>
       </c>
       <c r="J88" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K88" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L88">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+      <c r="M88" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B89" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C89" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D89" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E89" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F89" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G89" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H89" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I89">
         <v>260.29</v>
       </c>
       <c r="J89" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K89" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L89">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="M89" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B90" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C90" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D90" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E90" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F90" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G90" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H90" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I90">
         <v>218.51</v>
       </c>
       <c r="J90" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K90" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L90">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="M90" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B91" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C91" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D91" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E91" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F91" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G91" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H91" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I91">
         <v>525.97</v>
       </c>
       <c r="J91" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K91" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L91">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="M91" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B92" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C92" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D92" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E92" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F92" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G92" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H92" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I92">
         <v>446.53</v>
       </c>
       <c r="J92" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K92" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L92">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+      <c r="M92" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B93" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C93" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D93" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E93" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F93" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G93" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H93" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I93">
         <v>194.75</v>
       </c>
       <c r="J93" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K93" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L93">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+      <c r="M93" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B94" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C94" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D94" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E94" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F94" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G94" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H94" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I94">
         <v>320.67</v>
       </c>
       <c r="J94" t="s">
+        <v>21</v>
+      </c>
+      <c r="K94" t="s">
+        <v>22</v>
+      </c>
+      <c r="L94">
+        <v>94</v>
+      </c>
+      <c r="M94" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>183</v>
+      </c>
+      <c r="B95" t="s">
+        <v>48</v>
+      </c>
+      <c r="C95" t="s">
+        <v>184</v>
+      </c>
+      <c r="D95" t="s">
+        <v>36</v>
+      </c>
+      <c r="E95" t="s">
+        <v>17</v>
+      </c>
+      <c r="F95" t="s">
+        <v>56</v>
+      </c>
+      <c r="G95" t="s">
+        <v>50</v>
+      </c>
+      <c r="H95" t="s">
         <v>20</v>
-      </c>
-      <c r="K94" t="s">
-        <v>21</v>
-      </c>
-      <c r="L94">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>182</v>
-      </c>
-      <c r="B95" t="s">
-        <v>47</v>
-      </c>
-      <c r="C95" t="s">
-        <v>183</v>
-      </c>
-      <c r="D95" t="s">
-        <v>35</v>
-      </c>
-      <c r="E95" t="s">
-        <v>16</v>
-      </c>
-      <c r="F95" t="s">
-        <v>55</v>
-      </c>
-      <c r="G95" t="s">
-        <v>49</v>
-      </c>
-      <c r="H95" t="s">
-        <v>19</v>
       </c>
       <c r="I95">
         <v>261.54</v>
       </c>
       <c r="J95" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K95" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L95">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="M95" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B96" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C96" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D96" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E96" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F96" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G96" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H96" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I96">
         <v>267</v>
       </c>
       <c r="J96" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K96" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L96">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="M96" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B97" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C97" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D97" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E97" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F97" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G97" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H97" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I97">
         <v>232.79</v>
       </c>
       <c r="J97" t="s">
+        <v>21</v>
+      </c>
+      <c r="K97" t="s">
+        <v>22</v>
+      </c>
+      <c r="L97">
+        <v>95</v>
+      </c>
+      <c r="M97" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>187</v>
+      </c>
+      <c r="B98" t="s">
+        <v>54</v>
+      </c>
+      <c r="C98" t="s">
+        <v>188</v>
+      </c>
+      <c r="D98" t="s">
+        <v>43</v>
+      </c>
+      <c r="E98" t="s">
+        <v>26</v>
+      </c>
+      <c r="F98" t="s">
+        <v>56</v>
+      </c>
+      <c r="G98" t="s">
+        <v>45</v>
+      </c>
+      <c r="H98" t="s">
         <v>20</v>
-      </c>
-      <c r="K97" t="s">
-        <v>21</v>
-      </c>
-      <c r="L97">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>186</v>
-      </c>
-      <c r="B98" t="s">
-        <v>53</v>
-      </c>
-      <c r="C98" t="s">
-        <v>187</v>
-      </c>
-      <c r="D98" t="s">
-        <v>42</v>
-      </c>
-      <c r="E98" t="s">
-        <v>25</v>
-      </c>
-      <c r="F98" t="s">
-        <v>55</v>
-      </c>
-      <c r="G98" t="s">
-        <v>44</v>
-      </c>
-      <c r="H98" t="s">
-        <v>19</v>
       </c>
       <c r="I98">
         <v>459.49</v>
       </c>
       <c r="J98" t="s">
+        <v>21</v>
+      </c>
+      <c r="K98" t="s">
+        <v>22</v>
+      </c>
+      <c r="L98">
+        <v>96</v>
+      </c>
+      <c r="M98" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>187</v>
+      </c>
+      <c r="B99" t="s">
+        <v>41</v>
+      </c>
+      <c r="C99" t="s">
+        <v>189</v>
+      </c>
+      <c r="D99" t="s">
+        <v>39</v>
+      </c>
+      <c r="E99" t="s">
+        <v>26</v>
+      </c>
+      <c r="F99" t="s">
+        <v>56</v>
+      </c>
+      <c r="G99" t="s">
+        <v>37</v>
+      </c>
+      <c r="H99" t="s">
         <v>20</v>
-      </c>
-      <c r="K98" t="s">
-        <v>21</v>
-      </c>
-      <c r="L98">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>186</v>
-      </c>
-      <c r="B99" t="s">
-        <v>40</v>
-      </c>
-      <c r="C99" t="s">
-        <v>188</v>
-      </c>
-      <c r="D99" t="s">
-        <v>38</v>
-      </c>
-      <c r="E99" t="s">
-        <v>25</v>
-      </c>
-      <c r="F99" t="s">
-        <v>55</v>
-      </c>
-      <c r="G99" t="s">
-        <v>36</v>
-      </c>
-      <c r="H99" t="s">
-        <v>19</v>
       </c>
       <c r="I99">
         <v>405.86</v>
       </c>
       <c r="J99" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K99" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L99">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+      <c r="M99" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B100" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C100" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D100" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E100" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F100" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G100" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H100" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I100">
         <v>187.57</v>
       </c>
       <c r="J100" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K100" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L100">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+      <c r="M100" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B101" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C101" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D101" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E101" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F101" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G101" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H101" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I101">
         <v>535.83</v>
       </c>
       <c r="J101" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K101" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L101">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+      <c r="M101" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B102" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C102" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D102" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E102" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F102" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G102" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H102" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I102">
         <v>243.53</v>
       </c>
       <c r="J102" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K102" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L102">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+      <c r="M102" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B103" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C103" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D103" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E103" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F103" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G103" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H103" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I103">
         <v>282.32</v>
       </c>
       <c r="J103" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K103" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L103">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+      <c r="M103" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B104" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C104" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D104" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E104" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F104" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G104" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H104" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I104">
         <v>322.25</v>
       </c>
       <c r="J104" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K104" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L104">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="M104" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B105" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C105" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D105" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E105" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F105" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G105" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H105" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I105">
         <v>497.17</v>
       </c>
       <c r="J105" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K105" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L105">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="M105" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B106" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C106" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D106" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E106" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F106" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G106" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H106" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I106">
         <v>414.63</v>
       </c>
       <c r="J106" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K106" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L106">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="M106" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B107" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C107" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D107" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E107" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F107" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G107" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H107" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I107">
         <v>234.13</v>
       </c>
       <c r="J107" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K107" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L107">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="M107" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B108" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C108" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D108" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E108" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F108" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G108" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H108" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I108">
         <v>533.2</v>
       </c>
       <c r="J108" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K108" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L108">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="M108" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B109" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C109" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D109" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E109" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F109" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G109" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H109" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I109">
         <v>259.47</v>
       </c>
       <c r="J109" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K109" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L109">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="M109" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B110" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C110" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D110" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E110" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F110" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G110" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H110" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I110">
         <v>316.67</v>
       </c>
       <c r="J110" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K110" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L110">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="M110" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B111" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C111" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D111" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E111" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F111" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G111" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H111" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I111">
         <v>496.52</v>
       </c>
       <c r="J111" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K111" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L111">
-        <v>68</v>
+        <v>100</v>
+      </c>
+      <c r="M111" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:M1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -5266,17 +5602,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="30" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="12" max="13" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5313,389 +5649,422 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2">
         <v>209.91</v>
       </c>
       <c r="J2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L2">
+        <v>52</v>
+      </c>
+      <c r="M2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" t="s">
-        <v>19</v>
       </c>
       <c r="I3">
         <v>201.45</v>
       </c>
       <c r="J3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="M3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I4">
         <v>493.73</v>
       </c>
       <c r="J4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L4">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="M4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I5">
         <v>487.74</v>
       </c>
       <c r="J5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L5">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="M5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I6">
         <v>190.06</v>
       </c>
       <c r="J6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L6">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="M6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I7">
         <v>208.52</v>
       </c>
       <c r="J7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L7">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="M7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I8">
         <v>464.55</v>
       </c>
       <c r="J8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L8">
+        <v>88</v>
+      </c>
+      <c r="M8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>164</v>
-      </c>
-      <c r="B9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
       <c r="G9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I9">
         <v>480.01</v>
       </c>
       <c r="J9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L9">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="M9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I10">
         <v>470.62</v>
       </c>
       <c r="J10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L10">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+      <c r="M10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I11">
         <v>206.45</v>
       </c>
       <c r="J11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L11">
-        <v>68</v>
+        <v>100</v>
+      </c>
+      <c r="M11" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:M1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
